--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -22317,42 +22317,42 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu2fwwc6-0</t>
         </is>
       </c>
     </row>
@@ -22399,42 +22399,42 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu2fwwc6-1</t>
         </is>
       </c>
     </row>
@@ -22481,42 +22481,42 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -22526,7 +22526,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -22536,7 +22536,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-mu2fwwc6-2</t>
         </is>
       </c>
     </row>
@@ -22568,32 +22568,32 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22650,32 +22650,32 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22732,32 +22732,32 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22814,17 +22814,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22896,32 +22896,32 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -22998,12 +22998,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23060,57 +23060,57 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23142,17 +23142,17 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -23162,37 +23162,37 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23224,57 +23224,57 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23306,12 +23306,12 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23388,17 +23388,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23408,12 +23408,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23470,17 +23470,17 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -23490,12 +23490,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23552,17 +23552,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -23572,12 +23572,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23716,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23736,12 +23736,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23798,37 +23798,42 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23843,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23853,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23875,42 +23880,42 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -23925,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23935,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23957,12 +23962,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -23992,7 +23997,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -24017,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24039,17 +24044,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24059,12 +24064,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -24089,7 +24089,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24121,17 +24121,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24141,12 +24141,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24203,17 +24203,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24285,17 +24285,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24305,12 +24305,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24367,32 +24367,32 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24449,17 +24449,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24469,12 +24469,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24531,57 +24531,57 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24613,57 +24613,57 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24695,57 +24695,57 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24777,39 +24777,39 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24817,17 +24817,17 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24859,39 +24859,39 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24899,17 +24899,17 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24941,7 +24941,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24961,12 +24961,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25023,17 +25023,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -25043,12 +25043,12 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25063,17 +25063,17 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25105,32 +25105,32 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25145,17 +25145,17 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25187,32 +25187,32 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25269,17 +25269,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25289,37 +25289,37 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25351,57 +25351,57 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25433,17 +25433,17 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -25453,37 +25453,37 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25515,12 +25515,12 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25597,32 +25597,32 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,12 +25699,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25761,32 +25761,32 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25843,32 +25843,32 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25925,7 +25925,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -25935,7 +25935,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -25945,12 +25945,12 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26007,37 +26007,37 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26089,17 +26089,17 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -26109,22 +26109,22 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,22 +26191,22 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26253,17 +26253,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26417,22 +26417,22 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26499,32 +26499,32 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26581,32 +26581,32 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26663,42 +26663,42 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+7</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26765,22 +26765,22 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26790,22 +26790,12 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26815,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26837,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26857,22 +26847,22 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26882,22 +26872,12 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26907,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26929,37 +26909,37 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -26974,12 +26954,12 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26989,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27011,12 +26991,12 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -27061,7 +27041,17 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27071,7 +27061,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27093,32 +27083,32 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27138,12 +27128,22 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27175,32 +27175,32 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27220,12 +27220,12 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27235,7 +27235,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27257,32 +27257,32 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27302,12 +27302,12 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27317,7 +27317,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27339,27 +27339,32 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27379,7 +27384,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -27394,7 +27399,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27416,32 +27421,32 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27461,7 +27466,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -27476,7 +27481,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27498,17 +27503,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27518,22 +27523,22 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27548,7 +27553,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27558,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27580,42 +27585,37 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27625,12 +27625,12 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27662,42 +27662,42 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27707,12 +27707,12 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27722,7 +27722,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27744,17 +27744,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27826,12 +27826,12 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -27846,12 +27846,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27908,32 +27908,32 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27953,12 +27953,12 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -27990,12 +27990,12 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -28010,12 +28010,12 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28072,17 +28072,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28092,12 +28092,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28154,32 +28154,32 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28199,12 +28199,12 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28236,57 +28236,57 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28318,57 +28318,57 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28400,57 +28400,57 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28502,12 +28502,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28564,7 +28564,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28728,39 +28728,39 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28768,17 +28768,17 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28810,32 +28810,32 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -28850,17 +28850,17 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28892,290 +28892,350 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
+          <t xml:space="preserve">I6</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DtxR</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g1.1</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-160</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr">
+      <c r="E353" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
+      <c r="F353" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
+      <c r="G353" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
+      <c r="H353" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr">
+      <c r="I353" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr">
+      <c r="K353" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M350" t="inlineStr">
+      <c r="L353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N350" t="inlineStr">
+      <c r="N353" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O350" t="inlineStr">
+      <c r="O353" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R350" t="inlineStr">
+      <c r="R353" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S350" t="inlineStr">
+      <c r="S353" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="E351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="E352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="E353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -29200,19 +29260,19 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -29237,7 +29297,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -29252,7 +29312,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29262,19 +29322,19 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -29294,12 +29354,12 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -29314,7 +29374,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29324,19 +29384,19 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -29356,12 +29416,12 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -29386,19 +29446,19 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29418,12 +29478,12 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -29448,19 +29508,19 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -29485,7 +29545,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -29500,7 +29560,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -29510,19 +29570,19 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -29532,22 +29592,22 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -29557,7 +29617,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -29572,34 +29632,44 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -29624,34 +29694,44 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -29676,19 +29756,24 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -29701,6 +29786,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29713,7 +29803,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -29728,14 +29818,14 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -29755,7 +29845,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -29780,14 +29870,14 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -29832,14 +29922,14 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -29849,12 +29939,12 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -29884,14 +29974,14 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -29901,12 +29991,12 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -29936,14 +30026,14 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -29953,12 +30043,12 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -29988,62 +30078,218 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="E370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="E371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="E372" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
+      <c r="G372" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
+      <c r="H372" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr">
+      <c r="I372" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr">
+      <c r="K372" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M369" t="inlineStr">
+      <c r="L372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R369" t="inlineStr">
+      <c r="N372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S369" t="inlineStr">
+      <c r="S372" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -30189,12 +30435,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -30220,12 +30466,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -30239,7 +30485,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -30251,7 +30497,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -30270,24 +30516,24 @@
         </is>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK ATP7B-GFP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -30307,18 +30553,18 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -36643,10 +36889,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J6">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -22588,17 +22588,17 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu2fxi62-0</t>
         </is>
       </c>
     </row>
@@ -22645,22 +22645,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -22670,17 +22670,17 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu2fxi62-1</t>
         </is>
       </c>
     </row>
@@ -22727,42 +22727,42 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-mu2fxi62-2</t>
         </is>
       </c>
     </row>
@@ -22814,32 +22814,32 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22896,32 +22896,32 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22978,32 +22978,32 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23060,17 +23060,17 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -23080,12 +23080,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23142,32 +23142,32 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23224,7 +23224,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23244,12 +23244,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23306,57 +23306,57 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23388,17 +23388,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23408,37 +23408,37 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23470,57 +23470,57 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23552,12 +23552,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23634,17 +23634,17 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -23654,12 +23654,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23669,7 +23669,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23716,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23736,12 +23736,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23798,17 +23798,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23818,12 +23818,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23880,12 +23880,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23962,17 +23962,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23982,12 +23982,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24044,37 +24044,42 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -24089,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24099,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24121,42 +24126,42 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -24171,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24181,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24203,12 +24208,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24238,7 +24243,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -24263,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24285,17 +24290,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24305,12 +24310,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24367,17 +24367,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24387,12 +24387,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24449,17 +24449,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24469,12 +24469,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24531,17 +24531,17 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24551,12 +24551,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24613,32 +24613,32 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24695,17 +24695,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24715,12 +24715,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24777,57 +24777,57 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24859,57 +24859,57 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24941,57 +24941,57 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25023,39 +25023,39 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25063,17 +25063,17 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25105,39 +25105,39 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25145,17 +25145,17 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25269,17 +25269,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25289,12 +25289,12 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25309,17 +25309,17 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25351,32 +25351,32 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25391,17 +25391,17 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25433,32 +25433,32 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25535,37 +25535,37 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25597,57 +25597,57 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,37 +25699,37 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25761,12 +25761,12 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25843,32 +25843,32 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25925,17 +25925,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -25945,12 +25945,12 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26007,32 +26007,32 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26171,7 +26171,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,12 +26191,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26253,37 +26253,37 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,22 +26355,22 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26417,17 +26417,17 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -26437,22 +26437,22 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26663,22 +26663,22 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -26698,7 +26698,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26745,32 +26745,32 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26827,32 +26827,32 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26909,42 +26909,42 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+7</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27011,22 +27011,22 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27036,22 +27036,12 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27061,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27083,17 +27073,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27103,22 +27093,22 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27128,22 +27118,12 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27153,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27175,37 +27155,37 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -27220,12 +27200,12 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27235,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27257,12 +27237,12 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -27307,7 +27287,17 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27317,7 +27307,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27339,32 +27329,32 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27384,12 +27374,22 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27399,7 +27399,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27421,32 +27421,32 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27466,12 +27466,12 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27503,32 +27503,32 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27548,12 +27548,12 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27585,27 +27585,32 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27625,7 +27630,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -27640,7 +27645,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27662,32 +27667,32 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27707,7 +27712,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -27722,7 +27727,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27744,17 +27749,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -27764,22 +27769,22 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27794,7 +27799,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27804,7 +27809,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27826,42 +27831,37 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27871,12 +27871,12 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27908,42 +27908,42 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27953,12 +27953,12 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27990,17 +27990,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28072,12 +28072,12 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -28092,12 +28092,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28122,7 +28122,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28154,32 +28154,32 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28199,12 +28199,12 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28236,12 +28236,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -28256,12 +28256,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28318,17 +28318,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28338,12 +28338,12 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28353,7 +28353,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28400,32 +28400,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -28445,12 +28445,12 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28482,57 +28482,57 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28564,57 +28564,57 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28646,57 +28646,57 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28728,7 +28728,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28748,12 +28748,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28974,39 +28974,39 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29014,17 +29014,17 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29056,32 +29056,32 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29096,17 +29096,17 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29138,290 +29138,350 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
+          <t xml:space="preserve">I6</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DtxR</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g1.1</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-160</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
+      <c r="E356" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr">
+      <c r="F356" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
+      <c r="G356" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
+      <c r="H356" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr">
+      <c r="I356" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr">
+      <c r="K356" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
+      <c r="L356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr">
+      <c r="N356" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O353" t="inlineStr">
+      <c r="O356" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R353" t="inlineStr">
+      <c r="R356" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S353" t="inlineStr">
+      <c r="S356" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="E354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="E355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="E356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="M356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -29446,19 +29506,19 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29483,7 +29543,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -29498,7 +29558,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -29508,19 +29568,19 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -29540,12 +29600,12 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -29560,7 +29620,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -29570,19 +29630,19 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -29602,12 +29662,12 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -29632,19 +29692,19 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -29664,12 +29724,12 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -29694,19 +29754,19 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -29731,7 +29791,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -29746,7 +29806,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -29756,19 +29816,19 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -29778,22 +29838,22 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -29803,7 +29863,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -29818,34 +29878,44 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -29870,34 +29940,44 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -29922,19 +30002,24 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -29947,6 +30032,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29959,7 +30049,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -29974,14 +30064,14 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -30001,7 +30091,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -30026,14 +30116,14 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -30078,14 +30168,14 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -30095,12 +30185,12 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -30130,14 +30220,14 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -30147,12 +30237,12 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -30182,14 +30272,14 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -30199,12 +30289,12 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -30234,62 +30324,218 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="E373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="E374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="E375" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr">
+      <c r="G375" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
+      <c r="H375" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr">
+      <c r="I375" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr">
+      <c r="K375" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M372" t="inlineStr">
+      <c r="L375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R372" t="inlineStr">
+      <c r="N375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S372" t="inlineStr">
+      <c r="S375" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -30590,38 +30836,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -30636,38 +30882,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="E12">
@@ -30677,13 +30923,13 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -30693,12 +30939,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E13">
@@ -30708,44 +30954,44 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -30760,7 +31006,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E15">
@@ -30776,22 +31022,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E16">
@@ -30801,7 +31047,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -36889,10 +37135,10 @@
         <v>81</v>
       </c>
       <c r="I6">
+        <v>42</v>
+      </c>
+      <c r="J6">
         <v>39</v>
-      </c>
-      <c r="J6">
-        <v>42</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -35223,7 +35223,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -35270,7 +35270,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -35317,7 +35317,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -35505,7 +35505,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -36022,7 +36022,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -36069,7 +36069,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -36163,7 +36163,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -36210,7 +36210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -36257,7 +36257,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -36304,7 +36304,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -36351,7 +36351,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -36398,7 +36398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -36586,7 +36586,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -36633,7 +36633,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -36680,7 +36680,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -36727,7 +36727,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -36821,7 +36821,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -36868,7 +36868,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37181,12 +37181,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37191,7 +37191,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -37228,7 +37228,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37191,7 +37191,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -37265,7 +37265,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37191,7 +37191,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -37218,17 +37218,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -37265,7 +37265,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37191,7 +37191,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -37223,12 +37223,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37186,12 +37186,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -37228,7 +37228,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37255,12 +37255,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37292,12 +37292,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37329,12 +37329,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37366,12 +37366,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37403,17 +37403,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -37450,7 +37450,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -37487,7 +37487,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -37524,7 +37524,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -37561,7 +37561,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37181,17 +37181,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -37228,7 +37228,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -37265,7 +37265,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -37302,7 +37302,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -37339,7 +37339,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -37376,7 +37376,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -37440,17 +37440,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37218,17 +37218,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -37265,7 +37265,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -37302,7 +37302,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -37339,7 +37339,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -37376,7 +37376,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -37413,7 +37413,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -37445,12 +37445,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -37477,17 +37477,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37255,17 +37255,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -37302,7 +37302,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -37339,7 +37339,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -37376,7 +37376,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -37413,7 +37413,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -37450,7 +37450,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -37482,12 +37482,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -37514,17 +37514,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -37292,17 +37292,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 2</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baris Shelf</t>
+          <t xml:space="preserve">Rack 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -37339,7 +37339,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -37376,7 +37376,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -37413,7 +37413,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -37450,7 +37450,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -37487,7 +37487,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -37519,12 +37519,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Shelf</t>
+          <t xml:space="preserve">Baris Shelf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -37551,17 +37551,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Beyza Shelf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -22568,37 +22568,37 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-0</t>
+          <t xml:space="preserve">v-mu473zot-0</t>
         </is>
       </c>
     </row>
@@ -22650,37 +22650,37 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-1</t>
+          <t xml:space="preserve">v-mu473zot-1</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-2</t>
+          <t xml:space="preserve">v-mu2fxi62-0</t>
         </is>
       </c>
     </row>
@@ -22809,22 +22809,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22834,17 +22834,17 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu2fxi62-1</t>
         </is>
       </c>
     </row>
@@ -22891,22 +22891,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22916,17 +22916,17 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu2fxi62-2</t>
         </is>
       </c>
     </row>
@@ -22978,32 +22978,32 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23060,32 +23060,32 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23142,22 +23142,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23224,17 +23224,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23244,12 +23244,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23306,17 +23306,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -23326,12 +23326,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23388,22 +23388,22 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23470,12 +23470,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -23490,12 +23490,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23552,17 +23552,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -23572,37 +23572,37 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23634,57 +23634,57 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23716,12 +23716,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23798,12 +23798,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23880,17 +23880,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23900,12 +23900,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23962,17 +23962,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23982,12 +23982,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24044,12 +24044,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24208,12 +24208,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24290,37 +24290,42 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24335,7 +24340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24345,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24367,42 +24372,42 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -24417,7 +24422,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24449,17 +24454,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24469,12 +24474,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24531,17 +24531,17 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24551,12 +24551,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24613,17 +24613,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24695,17 +24695,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24715,12 +24715,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24777,12 +24777,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24859,32 +24859,32 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24941,17 +24941,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24961,12 +24961,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25023,17 +25023,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -25043,37 +25043,37 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25105,17 +25105,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25125,37 +25125,37 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25187,17 +25187,17 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25269,39 +25269,39 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25309,17 +25309,17 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25351,39 +25351,39 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25391,17 +25391,17 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25433,32 +25433,32 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25473,17 +25473,17 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25535,12 +25535,12 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25555,17 +25555,17 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,12 +25617,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,12 +25699,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25761,57 +25761,57 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25863,37 +25863,37 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25925,12 +25925,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26007,12 +26007,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,12 +26191,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26253,32 +26253,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26417,32 +26417,32 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,22 +26519,22 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26601,22 +26601,22 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26698,7 +26698,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26909,22 +26909,22 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26991,32 +26991,32 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27073,12 +27073,12 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -27093,12 +27093,12 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27155,42 +27155,42 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27237,17 +27237,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27257,22 +27257,22 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27282,22 +27282,12 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27307,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27329,37 +27319,37 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -27374,22 +27364,12 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27399,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27421,17 +27401,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27441,12 +27421,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27471,7 +27451,17 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27481,7 +27471,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27503,12 +27493,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -27553,7 +27543,17 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27585,32 +27585,32 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27630,12 +27630,12 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27667,32 +27667,32 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27712,12 +27712,12 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27749,12 +27749,12 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27831,27 +27831,32 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27871,7 +27876,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -27886,7 +27891,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27908,32 +27913,32 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27953,7 +27958,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -27968,7 +27973,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27990,42 +27995,37 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -28035,12 +28035,12 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28072,42 +28072,42 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28117,12 +28117,12 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28154,7 +28154,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28236,12 +28236,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -28256,12 +28256,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28318,17 +28318,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28353,7 +28353,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28400,32 +28400,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28445,12 +28445,12 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28482,12 +28482,12 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -28502,12 +28502,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28564,32 +28564,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28599,7 +28599,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28646,17 +28646,17 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28728,57 +28728,57 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28810,57 +28810,57 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28912,12 +28912,12 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29220,39 +29220,39 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29260,17 +29260,17 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29302,32 +29302,32 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -29342,17 +29342,17 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29384,228 +29384,268 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
+      <c r="E358" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
+      <c r="F358" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
+      <c r="G358" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
+      <c r="H358" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I356" t="inlineStr">
+      <c r="I358" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
+      <c r="K358" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M356" t="inlineStr">
+      <c r="L358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N356" t="inlineStr">
+      <c r="N358" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O356" t="inlineStr">
+      <c r="O358" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R356" t="inlineStr">
+      <c r="R358" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S356" t="inlineStr">
+      <c r="S358" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="E357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="E358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -29630,14 +29670,14 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -29667,7 +29707,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -29682,7 +29722,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -29692,19 +29732,19 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -29729,7 +29769,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -29754,19 +29794,19 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -29786,12 +29826,12 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -29806,7 +29846,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -29816,19 +29856,19 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -29848,12 +29888,12 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -29878,14 +29918,14 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -29915,7 +29955,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -29930,7 +29970,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -29940,14 +29980,14 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -29977,7 +30017,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -30002,19 +30042,19 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -30024,22 +30064,22 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -30049,7 +30089,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -30064,29 +30104,39 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -30116,19 +30166,24 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -30141,6 +30196,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30153,7 +30213,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -30168,14 +30228,14 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -30195,7 +30255,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -30220,7 +30280,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -30272,14 +30332,14 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -30324,14 +30384,14 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -30341,12 +30401,12 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -30376,14 +30436,14 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -30393,12 +30453,12 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -30428,7 +30488,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -30480,62 +30540,166 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="E376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="E377" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr">
+      <c r="G377" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
+      <c r="H377" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr">
+      <c r="I377" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr">
+      <c r="K377" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M375" t="inlineStr">
+      <c r="L377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N375" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O375" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R375" t="inlineStr">
+      <c r="N377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S375" t="inlineStr">
+      <c r="S377" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -31146,7 +31310,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -31161,7 +31325,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E20">
@@ -31171,18 +31335,18 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -31192,28 +31356,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">DuPar50CR+1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -31223,14 +31387,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E22">
         <v>4</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -31239,12 +31403,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -31254,28 +31418,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E23">
         <v>4</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -31285,7 +31449,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E24">
@@ -31295,18 +31459,18 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -31316,7 +31480,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E25">
@@ -31326,44 +31490,44 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">LUCX gP1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -31373,33 +31537,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -31409,7 +31573,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E28">
@@ -31425,17 +31589,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-I no sort</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -31450,13 +31614,13 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-K no sort</t>
+          <t xml:space="preserve">LCC-I no sort</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -31487,7 +31651,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-R no sort</t>
+          <t xml:space="preserve">LCC-K no sort</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -31518,7 +31682,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LCC-R no sort</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -31533,7 +31697,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E32">
@@ -31543,7 +31707,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -37135,10 +37299,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -22732,37 +22732,37 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-0</t>
+          <t xml:space="preserve">v-mu4747r6-0</t>
         </is>
       </c>
     </row>
@@ -22814,37 +22814,37 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-1</t>
+          <t xml:space="preserve">v-mu4747r6-1</t>
         </is>
       </c>
     </row>
@@ -22896,7 +22896,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-2</t>
+          <t xml:space="preserve">v-mu2fxi62-0</t>
         </is>
       </c>
     </row>
@@ -22973,22 +22973,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -22998,17 +22998,17 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -23018,7 +23018,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu2fxi62-1</t>
         </is>
       </c>
     </row>
@@ -23055,22 +23055,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -23080,17 +23080,17 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu2fxi62-2</t>
         </is>
       </c>
     </row>
@@ -23142,32 +23142,32 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23224,32 +23224,32 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23306,22 +23306,22 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23388,17 +23388,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23408,12 +23408,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23470,17 +23470,17 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -23490,12 +23490,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23552,22 +23552,22 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -23654,12 +23654,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23716,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23736,37 +23736,37 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23798,57 +23798,57 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23880,12 +23880,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23962,12 +23962,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -23997,7 +23997,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -24044,17 +24044,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24064,12 +24064,12 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24208,12 +24208,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24290,17 +24290,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24310,12 +24310,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24372,12 +24372,12 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24454,37 +24454,42 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -24499,7 +24504,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24531,42 +24536,42 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -24581,7 +24586,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24613,17 +24618,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24633,12 +24638,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24695,17 +24695,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24715,12 +24715,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24777,17 +24777,17 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24859,17 +24859,17 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -24879,12 +24879,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -25023,32 +25023,32 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -25105,17 +25105,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25125,12 +25125,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25187,17 +25187,17 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25207,37 +25207,37 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25269,17 +25269,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25289,37 +25289,37 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25351,17 +25351,17 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25433,39 +25433,39 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25473,17 +25473,17 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25515,39 +25515,39 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25555,17 +25555,17 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25597,32 +25597,32 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25637,17 +25637,17 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,12 +25699,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25719,17 +25719,17 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25761,17 +25761,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25781,12 +25781,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25863,12 +25863,12 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25925,57 +25925,57 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26007,17 +26007,17 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -26027,37 +26027,37 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -26089,12 +26089,12 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26171,12 +26171,12 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26253,32 +26253,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26417,32 +26417,32 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,12 +26519,12 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26581,32 +26581,32 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26683,22 +26683,22 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26765,22 +26765,22 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26909,17 +26909,17 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -27073,22 +27073,22 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -27155,32 +27155,32 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27237,12 +27237,12 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -27257,12 +27257,12 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27319,42 +27319,42 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27401,17 +27401,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27421,22 +27421,22 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27446,22 +27446,12 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27471,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27493,37 +27483,37 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -27538,22 +27528,12 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27563,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27585,17 +27565,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27605,12 +27585,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27635,7 +27615,17 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27645,7 +27635,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27667,12 +27657,12 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -27717,7 +27707,17 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27749,32 +27749,32 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27794,12 +27794,12 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27831,32 +27831,32 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27876,12 +27876,12 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27913,12 +27913,12 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27995,27 +27995,32 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28035,7 +28040,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -28050,7 +28055,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -28072,32 +28077,32 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28117,7 +28122,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -28132,7 +28137,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -28154,42 +28159,37 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28199,12 +28199,12 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28236,42 +28236,42 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -28281,12 +28281,12 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28318,7 +28318,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28400,12 +28400,12 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -28420,12 +28420,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28482,17 +28482,17 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28564,32 +28564,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28646,12 +28646,12 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -28666,12 +28666,12 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -28681,7 +28681,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28728,32 +28728,32 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28763,7 +28763,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -28773,12 +28773,12 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28810,17 +28810,17 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -28860,7 +28860,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28892,57 +28892,57 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28974,57 +28974,57 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -29076,12 +29076,12 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29220,7 +29220,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29384,39 +29384,39 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29424,17 +29424,17 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29466,32 +29466,32 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
@@ -29506,17 +29506,17 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29548,228 +29548,268 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
+      <c r="E360" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
+      <c r="F360" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
+      <c r="G360" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
+      <c r="H360" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr">
+      <c r="I360" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr">
+      <c r="K360" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M358" t="inlineStr">
+      <c r="L360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N358" t="inlineStr">
+      <c r="N360" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O358" t="inlineStr">
+      <c r="O360" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R358" t="inlineStr">
+      <c r="R360" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S358" t="inlineStr">
+      <c r="S360" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="E359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="E360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -29794,14 +29834,14 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -29831,7 +29871,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -29846,7 +29886,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -29856,19 +29896,19 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -29893,7 +29933,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -29918,19 +29958,19 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -29950,12 +29990,12 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -29970,7 +30010,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -29980,19 +30020,19 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -30012,12 +30052,12 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -30042,14 +30082,14 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -30079,7 +30119,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -30094,7 +30134,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -30104,14 +30144,14 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -30141,7 +30181,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -30166,19 +30206,19 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -30188,22 +30228,22 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -30213,7 +30253,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -30228,29 +30268,39 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -30280,19 +30330,24 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -30305,6 +30360,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30317,7 +30377,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -30332,14 +30392,14 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -30359,7 +30419,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -30384,7 +30444,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -30436,14 +30496,14 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -30488,14 +30548,14 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -30505,12 +30565,12 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -30540,14 +30600,14 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -30557,12 +30617,12 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -30592,7 +30652,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -30644,62 +30704,166 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="E378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="E379" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr">
+      <c r="G379" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
+      <c r="H379" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr">
+      <c r="I379" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr">
+      <c r="K379" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M377" t="inlineStr">
+      <c r="L379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O377" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R377" t="inlineStr">
+      <c r="N379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S377" t="inlineStr">
+      <c r="S379" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -31155,38 +31319,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -31201,7 +31365,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E16">
@@ -31217,22 +31381,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E17">
@@ -31242,23 +31406,23 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO G1</t>
+          <t xml:space="preserve">LnCap Canada V1G1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -31267,19 +31431,19 @@
         </is>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO G1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -31289,7 +31453,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -31304,28 +31468,28 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">HEK TOX4 OX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E20">
@@ -31335,13 +31499,13 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -31356,7 +31520,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E21">
@@ -31366,7 +31530,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -37299,10 +37463,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -22896,37 +22896,37 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-0</t>
+          <t xml:space="preserve">v-mu474j9w-0</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-1</t>
+          <t xml:space="preserve">v-mu2fxi62-0</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-2</t>
+          <t xml:space="preserve">v-mu2fxi62-1</t>
         </is>
       </c>
     </row>
@@ -23137,22 +23137,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -23162,17 +23162,17 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu2fxi62-2</t>
         </is>
       </c>
     </row>
@@ -23224,7 +23224,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23306,32 +23306,32 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23388,22 +23388,22 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23552,17 +23552,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -23572,12 +23572,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23634,17 +23634,17 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23716,22 +23716,22 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23798,32 +23798,32 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23880,57 +23880,57 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23962,7 +23962,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -24044,12 +24044,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24079,7 +24079,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -24126,7 +24126,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -24208,17 +24208,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24228,12 +24228,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24290,17 +24290,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24310,12 +24310,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24372,17 +24372,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24392,12 +24392,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24454,12 +24454,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24536,12 +24536,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24618,37 +24618,42 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -24663,7 +24668,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24678,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24695,7 +24700,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -24705,7 +24710,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24715,12 +24720,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24777,12 +24777,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24859,17 +24859,17 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -24879,12 +24879,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24941,17 +24941,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24961,12 +24961,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -25023,12 +25023,12 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -25105,12 +25105,12 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -25187,32 +25187,32 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25269,22 +25269,22 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25351,57 +25351,57 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25433,22 +25433,22 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25515,22 +25515,22 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25597,39 +25597,39 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25637,17 +25637,17 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25679,7 +25679,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25761,32 +25761,32 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25801,17 +25801,17 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25843,22 +25843,22 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25925,32 +25925,32 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -26007,32 +26007,32 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26089,17 +26089,17 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -26109,37 +26109,37 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -26171,12 +26171,12 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26253,12 +26253,12 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26335,12 +26335,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26417,32 +26417,32 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26499,22 +26499,22 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26581,32 +26581,32 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26663,32 +26663,32 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -26698,7 +26698,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26765,12 +26765,12 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26847,22 +26847,22 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26909,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -27155,17 +27155,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -27237,22 +27237,22 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27319,17 +27319,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27339,12 +27339,12 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27421,12 +27421,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27483,42 +27483,42 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+7</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/5/2025</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27565,37 +27565,37 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -27610,22 +27610,12 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27635,7 +27625,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27657,7 +27647,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -27727,7 +27717,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27749,17 +27739,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -27769,12 +27759,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27799,7 +27789,17 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -27841,7 +27841,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -27851,12 +27851,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27913,32 +27913,32 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27958,12 +27958,12 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27995,12 +27995,12 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -28077,12 +28077,12 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -28137,7 +28137,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -28159,27 +28159,32 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28199,7 +28204,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -28214,7 +28219,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -28236,12 +28241,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -28256,12 +28261,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28318,42 +28318,42 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -28363,12 +28363,12 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28400,17 +28400,17 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28420,12 +28420,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28482,17 +28482,17 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28502,12 +28502,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28564,17 +28564,17 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -28599,7 +28599,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -28614,7 +28614,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28728,32 +28728,32 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28773,12 +28773,12 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28810,32 +28810,32 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -28845,7 +28845,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -28855,12 +28855,12 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28892,17 +28892,17 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28912,12 +28912,12 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28942,7 +28942,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28974,17 +28974,17 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -28994,12 +28994,12 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -29056,57 +29056,57 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -29148,7 +29148,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -29158,12 +29158,12 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -29220,7 +29220,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29548,39 +29548,39 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29588,17 +29588,17 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29630,22 +29630,22 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -29670,7 +29670,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29712,161 +29712,181 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
+      <c r="E361" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
+      <c r="F361" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
+      <c r="G361" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
+      <c r="H361" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr">
+      <c r="I361" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr">
+      <c r="K361" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
+      <c r="L361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N360" t="inlineStr">
+      <c r="N361" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O360" t="inlineStr">
+      <c r="O361" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R360" t="inlineStr">
+      <c r="R361" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S360" t="inlineStr">
+      <c r="S361" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="E361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -29886,7 +29906,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -29896,14 +29916,14 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -29933,7 +29953,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -29948,7 +29968,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -29958,14 +29978,14 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -29995,7 +30015,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -30020,19 +30040,19 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -30057,7 +30077,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -30082,19 +30102,19 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -30114,12 +30134,12 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -30134,7 +30154,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -30144,19 +30164,19 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -30181,7 +30201,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -30196,7 +30216,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -30206,19 +30226,19 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -30243,7 +30263,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -30268,19 +30288,19 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -30305,7 +30325,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -30330,19 +30350,19 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -30352,22 +30372,22 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -30377,7 +30397,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -30392,19 +30412,24 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -30417,9 +30442,14 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -30429,7 +30459,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -30444,14 +30474,14 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -30471,7 +30501,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -30496,7 +30526,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -30548,7 +30578,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
@@ -30600,14 +30630,14 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -30652,14 +30682,14 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -30669,12 +30699,12 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -30704,7 +30734,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -30756,7 +30786,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
@@ -30808,62 +30838,114 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmypa-0</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="E380" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr">
+      <c r="G380" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
+      <c r="H380" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I379" t="inlineStr">
+      <c r="I380" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr">
+      <c r="K380" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M379" t="inlineStr">
+      <c r="L380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O379" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R379" t="inlineStr">
+      <c r="N380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S379" t="inlineStr">
+      <c r="S380" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -34915,22 +34997,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="E131">
@@ -34946,7 +35013,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -34977,7 +35044,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -35008,7 +35075,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -35039,7 +35106,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -35070,7 +35137,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -35101,7 +35168,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -35132,7 +35199,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -35142,7 +35209,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -35163,7 +35230,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -35194,17 +35261,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -35225,7 +35292,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -35235,7 +35307,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E141">
@@ -35251,7 +35323,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -35261,7 +35333,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E142">
@@ -35277,23 +35349,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="F143">
         <v>0</v>
       </c>
-      <c r="F143">
+      <c r="G143">
         <v>1</v>
-      </c>
-      <c r="G143">
-        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="E144">
@@ -35309,14 +35391,14 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -35325,14 +35407,14 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -35341,24 +35423,14 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -35367,16 +35439,42 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
+        <v>3</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">klm ox</t>
+        </is>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
         <v>1</v>
       </c>
-      <c r="G148">
+      <c r="G149">
         <v>0</v>
       </c>
     </row>
@@ -37463,10 +37561,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -23219,42 +23219,42 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu474lbd-0</t>
         </is>
       </c>
     </row>
@@ -23306,7 +23306,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23388,32 +23388,32 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23470,22 +23470,22 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23552,7 +23552,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23634,17 +23634,17 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -23654,12 +23654,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23716,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23798,22 +23798,22 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23880,32 +23880,32 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23962,57 +23962,57 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -24044,7 +24044,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -24126,12 +24126,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -24208,7 +24208,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -24290,17 +24290,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24310,12 +24310,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24372,17 +24372,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24392,12 +24392,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24454,17 +24454,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24536,12 +24536,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24700,37 +24700,42 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24745,7 +24750,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24760,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24777,7 +24782,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -24787,7 +24792,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24797,12 +24802,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24859,12 +24859,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24941,17 +24941,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24961,12 +24961,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -25023,17 +25023,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -25043,12 +25043,12 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -25105,12 +25105,12 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -25187,12 +25187,12 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -25269,32 +25269,32 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25351,22 +25351,22 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25433,57 +25433,57 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25515,22 +25515,22 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25597,22 +25597,22 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25679,39 +25679,39 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25719,17 +25719,17 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25761,7 +25761,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25843,32 +25843,32 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25883,17 +25883,17 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25925,22 +25925,22 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -26007,32 +26007,32 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,37 +26191,37 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -26253,12 +26253,12 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26335,12 +26335,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26417,12 +26417,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26499,32 +26499,32 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26581,22 +26581,22 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26663,32 +26663,32 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -26698,7 +26698,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26745,32 +26745,32 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26847,12 +26847,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26909,17 +26909,17 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -26929,22 +26929,22 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -27073,17 +27073,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -27237,17 +27237,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -27319,22 +27319,22 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27401,17 +27401,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27421,12 +27421,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27436,7 +27436,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27483,7 +27483,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -27493,7 +27493,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27503,12 +27503,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27565,42 +27565,42 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+7</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/5/2025</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27647,37 +27647,37 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -27692,22 +27692,12 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27717,7 +27707,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27739,7 +27729,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -27809,7 +27799,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27831,17 +27821,17 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -27851,12 +27841,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27881,7 +27871,17 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27913,7 +27913,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -27923,7 +27923,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27933,12 +27933,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27995,32 +27995,32 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28040,12 +28040,12 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -28077,12 +28077,12 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -28137,7 +28137,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -28159,12 +28159,12 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -28219,7 +28219,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -28241,27 +28241,32 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28281,7 +28286,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -28296,7 +28301,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -28318,12 +28323,12 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -28338,12 +28343,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28400,42 +28400,42 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -28445,12 +28445,12 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28482,17 +28482,17 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28502,12 +28502,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28564,17 +28564,17 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -28584,12 +28584,12 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28646,17 +28646,17 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -28681,7 +28681,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28728,7 +28728,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28810,32 +28810,32 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -28855,12 +28855,12 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28892,32 +28892,32 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -28937,12 +28937,12 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28974,17 +28974,17 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -28994,12 +28994,12 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -29056,17 +29056,17 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -29076,12 +29076,12 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -29138,57 +29138,57 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -29220,7 +29220,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -29240,12 +29240,12 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29630,39 +29630,39 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29670,17 +29670,17 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -29752,7 +29752,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29794,161 +29794,181 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
+      <c r="E362" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr">
+      <c r="F362" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
+      <c r="G362" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
+      <c r="H362" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr">
+      <c r="I362" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr">
+      <c r="K362" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
+      <c r="L362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr">
+      <c r="N362" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O361" t="inlineStr">
+      <c r="O362" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R361" t="inlineStr">
+      <c r="R362" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S361" t="inlineStr">
+      <c r="S362" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="E362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -29968,7 +29988,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -29978,14 +29998,14 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -30015,7 +30035,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -30030,7 +30050,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -30040,14 +30060,14 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -30077,7 +30097,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -30102,19 +30122,19 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -30139,7 +30159,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -30164,19 +30184,19 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -30196,12 +30216,12 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -30216,7 +30236,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -30226,19 +30246,19 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -30263,7 +30283,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -30278,7 +30298,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -30288,19 +30308,19 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -30325,7 +30345,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -30350,19 +30370,19 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -30387,7 +30407,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -30412,19 +30432,19 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -30434,22 +30454,22 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -30459,7 +30479,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -30474,19 +30494,24 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -30499,9 +30524,14 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -30511,7 +30541,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -30526,14 +30556,14 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -30553,7 +30583,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -30578,7 +30608,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30660,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
@@ -30682,14 +30712,14 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -30734,14 +30764,14 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -30751,12 +30781,12 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -30786,7 +30816,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -30838,7 +30868,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
@@ -30890,62 +30920,114 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmypa-0</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="E380" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="E381" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr">
+      <c r="G381" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
+      <c r="H381" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr">
+      <c r="I381" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr">
+      <c r="K381" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M380" t="inlineStr">
+      <c r="L381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O380" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R380" t="inlineStr">
+      <c r="N381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S380" t="inlineStr">
+      <c r="S381" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -32734,22 +32816,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="E58">
@@ -32765,12 +32847,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -32780,7 +32862,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E59">
@@ -32796,7 +32878,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -32806,7 +32888,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -32827,7 +32909,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -32837,7 +32919,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -32858,7 +32940,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -32868,7 +32950,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -32883,13 +32965,13 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -32914,13 +32996,13 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -32945,13 +33027,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -32976,23 +33058,23 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -33001,7 +33083,7 @@
         </is>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -33013,7 +33095,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -33023,7 +33105,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -33044,7 +33126,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -33054,12 +33136,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E68">
@@ -33075,22 +33157,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E69">
@@ -33106,7 +33188,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -33116,12 +33198,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E70">
@@ -33137,7 +33219,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -33147,12 +33229,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E71">
@@ -33168,7 +33250,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -33178,12 +33260,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E72">
@@ -33199,7 +33281,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -33221,7 +33303,7 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -33230,7 +33312,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -33252,7 +33334,7 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -33261,7 +33343,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -33271,7 +33353,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -33292,7 +33374,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33323,7 +33405,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33345,7 +33427,7 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -33354,7 +33436,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -33376,7 +33458,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -33385,7 +33467,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -33416,7 +33498,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -33447,7 +33529,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -33457,7 +33539,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -33478,7 +33560,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -33509,7 +33591,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -33540,7 +33622,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -33550,12 +33632,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E84">
@@ -33571,7 +33653,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -33581,12 +33663,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E85">
@@ -33602,7 +33684,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -33612,12 +33694,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E86">
@@ -33633,7 +33715,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -33643,12 +33725,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E87">
@@ -33664,7 +33746,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -33679,7 +33761,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E88">
@@ -33695,7 +33777,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -33705,7 +33787,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -33726,7 +33808,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -33736,12 +33818,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E90">
@@ -33757,7 +33839,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -33772,7 +33854,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E91">
@@ -33788,7 +33870,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -33819,7 +33901,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -33834,7 +33916,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E93">
@@ -33850,7 +33932,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -33865,7 +33947,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E94">
@@ -33881,7 +33963,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -33896,7 +33978,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E95">
@@ -33912,7 +33994,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -33927,7 +34009,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E96">
@@ -33943,7 +34025,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -33958,7 +34040,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E97">
@@ -33974,7 +34056,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -33989,7 +34071,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E98">
@@ -34005,7 +34087,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -34036,7 +34118,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -34051,7 +34133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E100">
@@ -34067,7 +34149,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -34077,12 +34159,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E101">
@@ -34098,7 +34180,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -34108,12 +34190,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E102">
@@ -34129,7 +34211,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -34139,12 +34221,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E103">
@@ -34160,17 +34242,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -34191,7 +34273,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -34213,7 +34295,7 @@
         <v>1</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -34222,7 +34304,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -34244,7 +34326,7 @@
         <v>1</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -34253,7 +34335,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -34263,7 +34345,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -34284,7 +34366,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -34306,7 +34388,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -34315,7 +34397,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -34337,7 +34419,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -34346,7 +34428,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -34356,7 +34438,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -34377,7 +34459,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -34408,7 +34490,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -34418,12 +34500,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E112">
@@ -34439,7 +34521,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -34449,12 +34531,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E113">
@@ -34470,7 +34552,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -34485,7 +34567,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E114">
@@ -34501,7 +34583,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -34511,12 +34593,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E115">
@@ -34532,7 +34614,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -34547,7 +34629,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E116">
@@ -34563,7 +34645,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -34578,7 +34660,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E117">
@@ -34594,7 +34676,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -34604,12 +34686,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E118">
@@ -34625,7 +34707,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -34656,7 +34738,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -34671,7 +34753,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E120">
@@ -34687,7 +34769,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -34697,12 +34779,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E121">
@@ -34718,7 +34800,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -34733,7 +34815,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E122">
@@ -34749,7 +34831,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -34780,17 +34862,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C*</t>
+          <t xml:space="preserve">Huh7 lef1 OX</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -34811,7 +34893,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E</t>
+          <t xml:space="preserve">LCC-C*</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -34842,7 +34924,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H</t>
+          <t xml:space="preserve">LCC-E</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -34873,7 +34955,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LCC-H</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -34904,7 +34986,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -34935,7 +35017,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -34966,7 +35048,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -34997,7 +35079,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCAP BMK</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E131">
@@ -37561,10 +37658,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -23301,42 +23301,42 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC1</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu474xr1-0</t>
         </is>
       </c>
     </row>
@@ -23383,42 +23383,42 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu474y7n-0</t>
         </is>
       </c>
     </row>
@@ -23470,32 +23470,32 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23552,32 +23552,32 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23634,22 +23634,22 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23716,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23736,12 +23736,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23798,17 +23798,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23818,12 +23818,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23880,22 +23880,22 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23962,12 +23962,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -23982,12 +23982,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -24044,17 +24044,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24064,37 +24064,37 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -24126,57 +24126,57 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -24208,12 +24208,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -24290,12 +24290,12 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24325,7 +24325,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -24372,17 +24372,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24392,12 +24392,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -24454,17 +24454,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24536,12 +24536,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24618,17 +24618,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24638,12 +24638,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24700,12 +24700,12 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24782,37 +24782,42 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24827,7 +24832,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24842,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24859,42 +24864,42 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24909,7 +24914,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24924,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24941,17 +24946,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24961,12 +24966,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -25023,17 +25023,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -25043,12 +25043,12 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -25105,17 +25105,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25125,12 +25125,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -25187,17 +25187,17 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -25269,12 +25269,12 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -25351,32 +25351,32 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -25433,17 +25433,17 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -25453,12 +25453,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25535,37 +25535,37 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,37 +25617,37 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25761,39 +25761,39 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25801,17 +25801,17 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25843,39 +25843,39 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25883,17 +25883,17 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25925,32 +25925,32 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25965,17 +25965,17 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -26007,17 +26007,17 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -26027,12 +26027,12 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26047,17 +26047,17 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -26089,17 +26089,17 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -26109,12 +26109,12 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,12 +26191,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -26253,57 +26253,57 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,37 +26355,37 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -26417,12 +26417,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26499,12 +26499,12 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26581,32 +26581,32 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26745,32 +26745,32 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26847,12 +26847,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26909,32 +26909,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27011,22 +27011,22 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -27073,17 +27073,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27093,22 +27093,22 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -27155,17 +27155,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -27237,17 +27237,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -27319,17 +27319,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -27401,22 +27401,22 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -27436,7 +27436,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -27483,32 +27483,32 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27518,7 +27518,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27565,12 +27565,12 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -27585,12 +27585,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27647,42 +27647,42 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27729,17 +27729,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -27749,22 +27749,22 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27774,22 +27774,12 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27799,7 +27789,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27821,37 +27811,37 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -27866,22 +27856,12 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27891,7 +27871,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27913,17 +27893,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27933,12 +27913,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27963,7 +27943,17 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27973,7 +27963,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27995,12 +27985,12 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -28045,7 +28035,17 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -28077,32 +28077,32 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28137,7 +28137,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -28159,32 +28159,32 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28204,12 +28204,12 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28219,7 +28219,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -28241,12 +28241,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -28323,27 +28323,32 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28363,7 +28368,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -28378,7 +28383,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -28400,32 +28405,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28445,7 +28450,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -28460,7 +28465,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -28482,42 +28487,37 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -28527,12 +28527,12 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28564,42 +28564,42 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28728,12 +28728,12 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -28748,12 +28748,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28763,7 +28763,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -28778,7 +28778,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28810,17 +28810,17 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -28845,7 +28845,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -28860,7 +28860,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28892,32 +28892,32 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28937,12 +28937,12 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28974,12 +28974,12 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -28994,12 +28994,12 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -29056,32 +29056,32 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -29101,12 +29101,12 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -29138,17 +29138,17 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -29220,57 +29220,57 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -29302,57 +29302,57 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -29404,12 +29404,12 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29630,7 +29630,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29712,39 +29712,39 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29752,17 +29752,17 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29794,32 +29794,32 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -29834,17 +29834,17 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29876,228 +29876,268 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
+      <c r="E364" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr">
+      <c r="F364" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
+      <c r="G364" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
+      <c r="H364" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr">
+      <c r="I364" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr">
+      <c r="K364" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M362" t="inlineStr">
+      <c r="L364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr">
+      <c r="N364" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O362" t="inlineStr">
+      <c r="O364" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R362" t="inlineStr">
+      <c r="R364" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S362" t="inlineStr">
+      <c r="S364" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="E363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="E364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -30122,14 +30162,14 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -30159,7 +30199,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -30174,7 +30214,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -30184,19 +30224,19 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -30221,7 +30261,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -30246,19 +30286,19 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -30278,12 +30318,12 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -30298,7 +30338,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -30308,19 +30348,19 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -30340,12 +30380,12 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -30370,14 +30410,14 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -30407,7 +30447,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -30422,7 +30462,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -30432,14 +30472,14 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -30469,7 +30509,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -30494,19 +30534,19 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -30516,22 +30556,22 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -30541,7 +30581,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -30556,29 +30596,39 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -30608,19 +30658,24 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -30633,6 +30688,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30645,7 +30705,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -30660,14 +30720,14 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -30687,7 +30747,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -30712,7 +30772,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -30764,14 +30824,14 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -30816,14 +30876,14 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -30833,12 +30893,12 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -30868,14 +30928,14 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -30885,12 +30945,12 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -30920,7 +30980,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -30972,62 +31032,166 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="E382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="E383" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr">
+      <c r="G383" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
+      <c r="H383" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr">
+      <c r="I383" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr">
+      <c r="K383" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M381" t="inlineStr">
+      <c r="L383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N381" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O381" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R381" t="inlineStr">
+      <c r="N383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S381" t="inlineStr">
+      <c r="S383" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -32816,22 +32980,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gP3</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="E58">
@@ -32847,22 +32996,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="E59">
@@ -32878,12 +33027,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -32893,7 +33042,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E60">
@@ -32909,7 +33058,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -32919,7 +33068,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -32940,7 +33089,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -32950,7 +33099,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -32971,7 +33120,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -32981,7 +33130,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -32996,13 +33145,13 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -33027,13 +33176,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -33058,13 +33207,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -33089,23 +33238,23 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -33114,7 +33263,7 @@
         </is>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -33126,7 +33275,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -33136,7 +33285,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -33157,7 +33306,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -33167,12 +33316,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E69">
@@ -33188,22 +33337,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E70">
@@ -33219,7 +33368,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -33229,12 +33378,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E71">
@@ -33250,7 +33399,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -33260,12 +33409,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E72">
@@ -33281,7 +33430,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -33291,12 +33440,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E73">
@@ -33312,7 +33461,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -33334,7 +33483,7 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -33343,7 +33492,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -33365,7 +33514,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -33374,7 +33523,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33384,7 +33533,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -33405,7 +33554,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33436,7 +33585,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -33458,7 +33607,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -33467,7 +33616,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -33489,7 +33638,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -33498,7 +33647,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -33529,7 +33678,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -33560,7 +33709,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -33570,7 +33719,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -33591,7 +33740,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -33622,7 +33771,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -33653,7 +33802,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -33663,12 +33812,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E85">
@@ -33684,7 +33833,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -33694,12 +33843,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E86">
@@ -33715,7 +33864,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -33725,12 +33874,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E87">
@@ -33746,7 +33895,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -33756,12 +33905,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E88">
@@ -33777,7 +33926,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -33792,7 +33941,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E89">
@@ -33808,7 +33957,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -33818,7 +33967,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -33839,7 +33988,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -33849,12 +33998,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E91">
@@ -33870,7 +34019,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -33885,7 +34034,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E92">
@@ -33901,7 +34050,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -33932,7 +34081,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -33947,7 +34096,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E94">
@@ -33963,7 +34112,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -33978,7 +34127,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E95">
@@ -33994,7 +34143,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -34009,7 +34158,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E96">
@@ -34025,7 +34174,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -34040,7 +34189,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E97">
@@ -34056,7 +34205,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -34071,7 +34220,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E98">
@@ -34087,7 +34236,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -34102,7 +34251,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E99">
@@ -34118,7 +34267,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -34149,7 +34298,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -34164,7 +34313,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E101">
@@ -34180,7 +34329,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -34190,12 +34339,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E102">
@@ -34211,7 +34360,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -34221,12 +34370,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E103">
@@ -34242,7 +34391,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -34252,12 +34401,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E104">
@@ -34273,17 +34422,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -34304,7 +34453,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -34326,7 +34475,7 @@
         <v>1</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -34335,7 +34484,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -34357,7 +34506,7 @@
         <v>1</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -34366,7 +34515,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -34376,7 +34525,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -34397,7 +34546,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -34419,7 +34568,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -34428,7 +34577,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -34450,7 +34599,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -34459,7 +34608,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -34469,7 +34618,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -34490,7 +34639,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -34521,7 +34670,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -34531,12 +34680,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E113">
@@ -34552,7 +34701,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -34562,12 +34711,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E114">
@@ -34583,7 +34732,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -34598,7 +34747,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E115">
@@ -34614,7 +34763,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -34624,12 +34773,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E116">
@@ -34645,7 +34794,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -34660,7 +34809,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E117">
@@ -34676,7 +34825,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -34691,7 +34840,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E118">
@@ -34707,7 +34856,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -34717,12 +34866,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E119">
@@ -34738,7 +34887,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -34769,7 +34918,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -34784,7 +34933,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E121">
@@ -34800,7 +34949,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -34810,12 +34959,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E122">
@@ -34831,7 +34980,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -34846,7 +34995,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E123">
@@ -34862,7 +35011,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -34893,17 +35042,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C*</t>
+          <t xml:space="preserve">Huh7 lef1 OX</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -34924,7 +35073,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E</t>
+          <t xml:space="preserve">LCC-C*</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -34955,7 +35104,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H</t>
+          <t xml:space="preserve">LCC-E</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -34986,7 +35135,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LCC-H</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -35017,7 +35166,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -35048,7 +35197,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -35079,7 +35228,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -35110,7 +35259,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LNCAP BMK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -35141,7 +35290,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -35172,7 +35321,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -35203,7 +35352,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -35234,7 +35383,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -35265,7 +35414,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -35296,7 +35445,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -35327,7 +35476,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -35337,7 +35486,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -35358,7 +35507,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -35389,17 +35538,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -35420,7 +35569,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -35430,7 +35584,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E142">
@@ -35446,7 +35600,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -35456,7 +35610,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E143">
@@ -35472,23 +35626,33 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144">
         <v>0</v>
       </c>
-      <c r="F144">
+      <c r="G144">
         <v>1</v>
-      </c>
-      <c r="G144">
-        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="E145">
@@ -35504,14 +35668,14 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -35520,14 +35684,14 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -35536,24 +35700,14 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -35562,16 +35716,42 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
+        <v>3</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">klm ox</t>
+        </is>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+      <c r="F150">
         <v>1</v>
       </c>
-      <c r="G149">
+      <c r="G150">
         <v>0</v>
       </c>
     </row>
@@ -37658,10 +37838,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -23465,42 +23465,42 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -23510,7 +23510,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC2</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu475zr8-0</t>
         </is>
       </c>
     </row>
@@ -23547,42 +23547,42 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC2</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu475zr8-1</t>
         </is>
       </c>
     </row>
@@ -23634,32 +23634,32 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23716,32 +23716,32 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23798,22 +23798,22 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23880,17 +23880,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23900,12 +23900,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23962,17 +23962,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23982,12 +23982,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -24044,22 +24044,22 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -24126,12 +24126,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -24208,17 +24208,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24228,37 +24228,37 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -24290,57 +24290,57 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -24372,12 +24372,12 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -24454,12 +24454,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -24536,17 +24536,17 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24556,12 +24556,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -24618,17 +24618,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24638,12 +24638,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24700,12 +24700,12 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24782,17 +24782,17 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24802,12 +24802,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24864,12 +24864,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24946,37 +24946,42 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -24991,7 +24996,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25006,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -25023,42 +25028,42 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -25073,7 +25078,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25088,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -25105,17 +25110,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25125,12 +25130,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -25187,17 +25187,17 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25207,12 +25207,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -25269,17 +25269,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25289,12 +25289,12 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -25351,17 +25351,17 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -25371,12 +25371,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -25433,12 +25433,12 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -25468,7 +25468,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -25515,32 +25515,32 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,12 +25617,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,37 +25699,37 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25761,17 +25761,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25781,37 +25781,37 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25925,39 +25925,39 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25965,17 +25965,17 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -26007,39 +26007,39 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26047,17 +26047,17 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26129,17 +26129,17 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,12 +26191,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26211,17 +26211,17 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -26253,17 +26253,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -26273,12 +26273,12 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -26417,57 +26417,57 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,37 +26519,37 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -26581,12 +26581,12 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26663,12 +26663,12 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26745,32 +26745,32 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26847,12 +26847,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26909,32 +26909,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27011,12 +27011,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -27073,32 +27073,32 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -27155,17 +27155,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27175,22 +27175,22 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -27237,17 +27237,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27257,22 +27257,22 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -27319,17 +27319,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -27401,17 +27401,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27436,7 +27436,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -27483,17 +27483,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27518,7 +27518,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -27565,22 +27565,22 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -27647,32 +27647,32 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27729,12 +27729,12 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -27749,12 +27749,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27811,42 +27811,42 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27893,17 +27893,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27913,22 +27913,22 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27938,22 +27938,12 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27963,7 +27953,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27985,37 +27975,37 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -28030,22 +28020,12 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28055,7 +28035,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -28077,17 +28057,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28097,12 +28077,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28127,7 +28107,17 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28137,7 +28127,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -28159,12 +28149,12 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -28209,7 +28199,17 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28219,7 +28219,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -28241,32 +28241,32 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28286,12 +28286,12 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -28323,32 +28323,32 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -28405,12 +28405,12 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -28465,7 +28465,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -28487,27 +28487,32 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28527,7 +28532,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -28542,7 +28547,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -28564,32 +28569,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28609,7 +28614,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -28624,7 +28629,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -28646,42 +28651,37 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -28691,12 +28691,12 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28728,42 +28728,42 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -28773,12 +28773,12 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28892,12 +28892,12 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -28912,12 +28912,12 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -28942,7 +28942,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28974,17 +28974,17 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -29056,32 +29056,32 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29101,12 +29101,12 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -29138,12 +29138,12 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -29158,12 +29158,12 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -29220,32 +29220,32 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -29265,12 +29265,12 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -29302,17 +29302,17 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -29384,57 +29384,57 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -29466,57 +29466,57 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29568,12 +29568,12 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -29630,7 +29630,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29794,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29876,39 +29876,39 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29916,17 +29916,17 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29958,32 +29958,32 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -29998,17 +29998,17 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -30018,7 +30018,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -30040,228 +30040,268 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
+      <c r="E366" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
+      <c r="F366" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr">
+      <c r="G366" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
+      <c r="H366" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr">
+      <c r="I366" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr">
+      <c r="K366" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M364" t="inlineStr">
+      <c r="L366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N364" t="inlineStr">
+      <c r="N366" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O364" t="inlineStr">
+      <c r="O366" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R364" t="inlineStr">
+      <c r="R366" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S364" t="inlineStr">
+      <c r="S366" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="E365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="E366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -30286,14 +30326,14 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -30323,7 +30363,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -30338,7 +30378,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -30348,19 +30388,19 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -30385,7 +30425,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -30410,19 +30450,19 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -30442,12 +30482,12 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -30462,7 +30502,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -30472,19 +30512,19 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -30504,12 +30544,12 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -30534,14 +30574,14 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -30571,7 +30611,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -30586,7 +30626,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
@@ -30596,14 +30636,14 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -30633,7 +30673,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -30658,19 +30698,19 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -30680,22 +30720,22 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -30705,7 +30745,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -30720,29 +30760,39 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -30772,19 +30822,24 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -30797,6 +30852,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30809,7 +30869,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -30824,14 +30884,14 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -30851,7 +30911,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -30876,7 +30936,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -30928,14 +30988,14 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -30980,14 +31040,14 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="E380" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -30997,12 +31057,12 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -31032,14 +31092,14 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -31049,12 +31109,12 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -31084,7 +31144,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -31136,62 +31196,166 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="E383" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="E384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="E385" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr">
+      <c r="G385" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
+      <c r="H385" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr">
+      <c r="I385" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr">
+      <c r="K385" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M383" t="inlineStr">
+      <c r="L385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N383" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O383" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R383" t="inlineStr">
+      <c r="N385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S383" t="inlineStr">
+      <c r="S385" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -32996,22 +33160,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gP3</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="E59">
@@ -33027,22 +33176,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="E60">
@@ -33058,12 +33207,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -33073,7 +33222,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E61">
@@ -33089,7 +33238,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -33099,7 +33248,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -33120,7 +33269,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -33130,7 +33279,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -33151,7 +33300,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -33161,7 +33310,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33176,13 +33325,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -33207,13 +33356,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -33238,13 +33387,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -33269,23 +33418,23 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -33294,7 +33443,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -33306,7 +33455,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -33316,7 +33465,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -33337,7 +33486,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -33347,12 +33496,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E70">
@@ -33368,22 +33517,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E71">
@@ -33399,7 +33548,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -33409,12 +33558,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E72">
@@ -33430,7 +33579,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -33440,12 +33589,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E73">
@@ -33461,7 +33610,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -33471,12 +33620,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E74">
@@ -33492,7 +33641,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -33514,7 +33663,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -33523,7 +33672,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33545,7 +33694,7 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -33554,7 +33703,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33564,7 +33713,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -33585,7 +33734,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -33616,7 +33765,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -33638,7 +33787,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -33647,7 +33796,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -33669,7 +33818,7 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -33678,7 +33827,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -33709,7 +33858,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -33740,7 +33889,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -33750,7 +33899,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -33771,7 +33920,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -33802,7 +33951,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -33833,7 +33982,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -33843,12 +33992,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E86">
@@ -33864,7 +34013,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -33874,12 +34023,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E87">
@@ -33895,7 +34044,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -33905,12 +34054,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E88">
@@ -33926,7 +34075,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -33936,12 +34085,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E89">
@@ -33957,7 +34106,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -33972,7 +34121,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E90">
@@ -33988,7 +34137,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -33998,7 +34147,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -34019,7 +34168,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -34029,12 +34178,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E92">
@@ -34050,7 +34199,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -34065,7 +34214,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E93">
@@ -34081,7 +34230,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -34112,7 +34261,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -34127,7 +34276,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E95">
@@ -34143,7 +34292,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -34158,7 +34307,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E96">
@@ -34174,7 +34323,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -34189,7 +34338,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E97">
@@ -34205,7 +34354,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -34220,7 +34369,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E98">
@@ -34236,7 +34385,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -34251,7 +34400,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E99">
@@ -34267,7 +34416,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -34282,7 +34431,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E100">
@@ -34298,7 +34447,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -34329,7 +34478,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -34344,7 +34493,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E102">
@@ -34360,7 +34509,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -34370,12 +34519,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E103">
@@ -34391,7 +34540,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -34401,12 +34550,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E104">
@@ -34422,7 +34571,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -34432,12 +34581,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E105">
@@ -34453,17 +34602,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -34484,7 +34633,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -34506,7 +34655,7 @@
         <v>1</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -34515,7 +34664,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -34537,7 +34686,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -34546,7 +34695,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -34556,7 +34705,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -34577,7 +34726,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -34599,7 +34748,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -34608,7 +34757,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -34630,7 +34779,7 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -34639,7 +34788,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -34649,7 +34798,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -34670,7 +34819,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -34701,7 +34850,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -34711,12 +34860,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E114">
@@ -34732,7 +34881,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -34742,12 +34891,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E115">
@@ -34763,7 +34912,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -34778,7 +34927,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E116">
@@ -34794,7 +34943,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -34804,12 +34953,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E117">
@@ -34825,7 +34974,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -34840,7 +34989,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E118">
@@ -34856,7 +35005,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -34871,7 +35020,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E119">
@@ -34887,7 +35036,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -34897,12 +35046,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E120">
@@ -34918,7 +35067,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -34949,7 +35098,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -34964,7 +35113,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E122">
@@ -34980,7 +35129,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -34990,12 +35139,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E123">
@@ -35011,7 +35160,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -35026,7 +35175,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E124">
@@ -35042,7 +35191,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -35073,17 +35222,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C*</t>
+          <t xml:space="preserve">Huh7 lef1 OX</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -35104,7 +35253,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E</t>
+          <t xml:space="preserve">LCC-C*</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -35135,7 +35284,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H</t>
+          <t xml:space="preserve">LCC-E</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -35166,7 +35315,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LCC-H</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -35197,7 +35346,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -35228,7 +35377,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -35259,7 +35408,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -35290,7 +35439,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LNCAP BMK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -35321,7 +35470,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -35352,7 +35501,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -35383,7 +35532,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -35414,7 +35563,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -35445,7 +35594,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -35476,7 +35625,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -35507,7 +35656,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -35517,7 +35666,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -35538,7 +35687,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -35569,17 +35718,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -35600,7 +35749,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -35610,7 +35764,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E143">
@@ -35626,7 +35780,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -35636,7 +35790,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E144">
@@ -35652,23 +35806,33 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E145">
+        <v>1</v>
+      </c>
+      <c r="F145">
         <v>0</v>
       </c>
-      <c r="F145">
+      <c r="G145">
         <v>1</v>
-      </c>
-      <c r="G145">
-        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="E146">
@@ -35684,14 +35848,14 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -35700,14 +35864,14 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -35716,24 +35880,14 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -35742,16 +35896,42 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
+        <v>3</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">klm ox</t>
+        </is>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+      <c r="F151">
         <v>1</v>
       </c>
-      <c r="G150">
+      <c r="G151">
         <v>0</v>
       </c>
     </row>
@@ -37838,10 +38018,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -23629,42 +23629,42 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC3</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu4763vn-0</t>
         </is>
       </c>
     </row>
@@ -23711,42 +23711,42 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC3</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu4763vn-1</t>
         </is>
       </c>
     </row>
@@ -23798,32 +23798,32 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23880,32 +23880,32 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23962,22 +23962,22 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -24044,17 +24044,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24064,12 +24064,12 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -24208,22 +24208,22 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -24290,12 +24290,12 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24310,12 +24310,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -24372,17 +24372,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24392,37 +24392,37 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -24454,57 +24454,57 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -24536,12 +24536,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -24571,7 +24571,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -24618,12 +24618,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -24653,7 +24653,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -24700,17 +24700,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24720,12 +24720,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -24782,17 +24782,17 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24802,12 +24802,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24864,12 +24864,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24946,17 +24946,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24966,12 +24966,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -25028,12 +25028,12 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -25110,37 +25110,42 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -25155,7 +25160,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25170,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -25187,42 +25192,42 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -25237,7 +25242,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25252,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -25269,17 +25274,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25289,12 +25294,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -25351,17 +25351,17 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -25371,12 +25371,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -25433,17 +25433,17 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -25453,12 +25453,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25535,12 +25535,12 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -25597,12 +25597,12 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -25679,32 +25679,32 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -25761,17 +25761,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25781,12 +25781,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25863,37 +25863,37 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25925,17 +25925,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -25945,37 +25945,37 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -26007,17 +26007,17 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -26089,39 +26089,39 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26129,17 +26129,17 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -26171,39 +26171,39 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26211,17 +26211,17 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -26253,32 +26253,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26293,17 +26293,17 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26375,17 +26375,17 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -26417,17 +26417,17 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -26437,12 +26437,12 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,12 +26519,12 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -26581,57 +26581,57 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26683,37 +26683,37 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -26745,12 +26745,12 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26827,12 +26827,12 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26909,32 +26909,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27011,12 +27011,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -27073,32 +27073,32 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -27155,17 +27155,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27175,12 +27175,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -27237,32 +27237,32 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -27319,17 +27319,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27339,22 +27339,22 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -27401,17 +27401,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27421,22 +27421,22 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -27483,17 +27483,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27518,7 +27518,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -27565,17 +27565,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -27647,17 +27647,17 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -27729,22 +27729,22 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -27811,32 +27811,32 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27893,12 +27893,12 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -27913,12 +27913,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27953,7 +27953,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27975,42 +27975,42 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -28057,17 +28057,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28077,22 +28077,22 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28102,22 +28102,12 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P340" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q340" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28127,7 +28117,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -28149,37 +28139,37 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -28194,22 +28184,12 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28219,7 +28199,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -28241,17 +28221,17 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -28261,12 +28241,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28291,7 +28271,17 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28301,7 +28291,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -28323,12 +28313,12 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -28373,7 +28363,17 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -28405,32 +28405,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28450,12 +28450,12 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28465,7 +28465,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -28487,32 +28487,32 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28532,12 +28532,12 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -28569,12 +28569,12 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -28651,27 +28651,32 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -28691,7 +28696,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -28706,7 +28711,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -28728,32 +28733,32 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28773,7 +28778,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -28788,7 +28793,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -28810,42 +28815,37 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -28855,12 +28855,12 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28892,42 +28892,42 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -28937,12 +28937,12 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -29056,12 +29056,12 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -29076,12 +29076,12 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -29106,7 +29106,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -29138,17 +29138,17 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -29220,32 +29220,32 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -29265,12 +29265,12 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -29302,12 +29302,12 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -29384,32 +29384,32 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -29429,12 +29429,12 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -29466,17 +29466,17 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -29548,57 +29548,57 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -29630,57 +29630,57 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -29732,12 +29732,12 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29794,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29876,7 +29876,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29958,7 +29958,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -30018,7 +30018,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -30040,39 +30040,39 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30080,17 +30080,17 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -30100,7 +30100,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -30122,32 +30122,32 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -30162,17 +30162,17 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -30204,228 +30204,268 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E368" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
+      <c r="F368" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
+      <c r="G368" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
+      <c r="H368" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr">
+      <c r="I368" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr">
+      <c r="K368" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M366" t="inlineStr">
+      <c r="L368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr">
+      <c r="N368" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O366" t="inlineStr">
+      <c r="O368" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R366" t="inlineStr">
+      <c r="R368" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S366" t="inlineStr">
+      <c r="S368" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="E367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="E368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -30450,14 +30490,14 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -30487,7 +30527,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -30502,7 +30542,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -30512,19 +30552,19 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -30549,7 +30589,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -30574,19 +30614,19 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -30606,12 +30646,12 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -30626,7 +30666,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
@@ -30636,19 +30676,19 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -30668,12 +30708,12 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -30698,14 +30738,14 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -30735,7 +30775,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -30750,7 +30790,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
@@ -30760,14 +30800,14 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -30797,7 +30837,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -30822,19 +30862,19 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -30844,22 +30884,22 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -30869,7 +30909,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -30884,29 +30924,39 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -30936,19 +30986,24 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -30961,6 +31016,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30973,7 +31033,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -30988,14 +31048,14 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -31015,7 +31075,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -31040,7 +31100,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -31092,14 +31152,14 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -31144,14 +31204,14 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="E382" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -31161,12 +31221,12 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -31196,14 +31256,14 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -31213,12 +31273,12 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -31248,7 +31308,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -31300,62 +31360,166 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="E385" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="E386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="E387" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
+      <c r="G387" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
+      <c r="H387" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr">
+      <c r="I387" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
+      <c r="K387" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M385" t="inlineStr">
+      <c r="L387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N385" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O385" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R385" t="inlineStr">
+      <c r="N387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S385" t="inlineStr">
+      <c r="S387" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -33176,7 +33340,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -33191,7 +33355,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP3</t>
+          <t xml:space="preserve">gC3</t>
         </is>
       </c>
       <c r="E60">
@@ -33207,22 +33371,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="E61">
@@ -33238,12 +33402,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -33253,7 +33417,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E62">
@@ -33269,7 +33433,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -33279,7 +33443,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -33300,7 +33464,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -33310,7 +33474,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33331,7 +33495,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -33341,7 +33505,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -33356,13 +33520,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -33387,13 +33551,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -33418,13 +33582,13 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -33449,23 +33613,23 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -33474,7 +33638,7 @@
         </is>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -33486,7 +33650,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -33496,7 +33660,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -33517,7 +33681,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -33527,12 +33691,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E71">
@@ -33548,22 +33712,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E72">
@@ -33579,7 +33743,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -33589,12 +33753,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E73">
@@ -33610,7 +33774,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -33620,12 +33784,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E74">
@@ -33641,7 +33805,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -33651,12 +33815,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E75">
@@ -33672,7 +33836,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33694,7 +33858,7 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -33703,7 +33867,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33725,7 +33889,7 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -33734,7 +33898,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -33744,7 +33908,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -33765,7 +33929,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -33796,7 +33960,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -33818,7 +33982,7 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -33827,7 +33991,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -33849,7 +34013,7 @@
         <v>1</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -33858,7 +34022,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -33889,7 +34053,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -33920,7 +34084,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -33930,7 +34094,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -33951,7 +34115,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -33982,7 +34146,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -34013,7 +34177,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -34023,12 +34187,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E87">
@@ -34044,7 +34208,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -34054,12 +34218,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E88">
@@ -34075,7 +34239,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -34085,12 +34249,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E89">
@@ -34106,7 +34270,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -34116,12 +34280,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E90">
@@ -34137,7 +34301,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -34152,7 +34316,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E91">
@@ -34168,7 +34332,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -34178,7 +34342,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -34199,7 +34363,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -34209,12 +34373,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E93">
@@ -34230,7 +34394,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -34245,7 +34409,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E94">
@@ -34261,7 +34425,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -34292,7 +34456,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -34307,7 +34471,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E96">
@@ -34323,7 +34487,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -34338,7 +34502,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E97">
@@ -34354,7 +34518,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -34369,7 +34533,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E98">
@@ -34385,7 +34549,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -34400,7 +34564,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E99">
@@ -34416,7 +34580,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -34431,7 +34595,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E100">
@@ -34447,7 +34611,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -34462,7 +34626,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E101">
@@ -34478,7 +34642,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -34509,7 +34673,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -34524,7 +34688,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E103">
@@ -34540,7 +34704,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -34550,12 +34714,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E104">
@@ -34571,7 +34735,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -34581,12 +34745,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E105">
@@ -34602,7 +34766,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -34612,12 +34776,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E106">
@@ -34633,17 +34797,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -34664,7 +34828,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -34686,7 +34850,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -34695,7 +34859,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -34717,7 +34881,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -34726,7 +34890,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -34736,7 +34900,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -34757,7 +34921,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -34779,7 +34943,7 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -34788,7 +34952,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -34810,7 +34974,7 @@
         <v>1</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -34819,7 +34983,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -34829,7 +34993,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -34850,7 +35014,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -34881,7 +35045,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -34891,12 +35055,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E115">
@@ -34912,7 +35076,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -34922,12 +35086,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E116">
@@ -34943,7 +35107,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -34958,7 +35122,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E117">
@@ -34974,7 +35138,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -34984,12 +35148,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E118">
@@ -35005,7 +35169,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -35020,7 +35184,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E119">
@@ -35036,7 +35200,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -35051,7 +35215,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E120">
@@ -35067,7 +35231,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -35077,12 +35241,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E121">
@@ -35098,7 +35262,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -35129,7 +35293,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -35144,7 +35308,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E123">
@@ -35160,7 +35324,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -35170,12 +35334,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E124">
@@ -35191,7 +35355,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -35206,7 +35370,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E125">
@@ -35222,7 +35386,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -35253,17 +35417,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C*</t>
+          <t xml:space="preserve">Huh7 lef1 OX</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -35284,7 +35448,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E</t>
+          <t xml:space="preserve">LCC-C*</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -35315,7 +35479,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H</t>
+          <t xml:space="preserve">LCC-E</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -35346,7 +35510,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LCC-H</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -35377,7 +35541,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -35408,7 +35572,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -35439,7 +35603,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -35470,7 +35634,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LNCAP BMK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -35501,7 +35665,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -35532,7 +35696,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -35563,7 +35727,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -35594,7 +35758,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -35625,7 +35789,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -35656,7 +35820,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -35687,7 +35851,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -35697,7 +35861,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -35718,7 +35882,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -35749,17 +35913,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -35780,7 +35944,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -35790,7 +35959,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E144">
@@ -35806,7 +35975,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -35816,7 +35985,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E145">
@@ -35832,23 +36001,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E146">
+        <v>1</v>
+      </c>
+      <c r="F146">
         <v>0</v>
       </c>
-      <c r="F146">
+      <c r="G146">
         <v>1</v>
-      </c>
-      <c r="G146">
-        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="E147">
@@ -35864,14 +36043,14 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -35880,14 +36059,14 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -35896,24 +36075,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -35922,16 +36091,42 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
+        <v>3</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">klm ox</t>
+        </is>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152">
         <v>1</v>
       </c>
-      <c r="G151">
+      <c r="G152">
         <v>0</v>
       </c>
     </row>
@@ -38018,10 +38213,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -23793,42 +23793,42 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -23838,7 +23838,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC4</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu47689b-0</t>
         </is>
       </c>
     </row>
@@ -23875,42 +23875,42 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC4</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-mu47689b-1</t>
         </is>
       </c>
     </row>
@@ -23962,32 +23962,32 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -24044,32 +24044,32 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -24126,22 +24126,22 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -24208,17 +24208,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24228,12 +24228,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -24290,17 +24290,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24310,12 +24310,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -24372,22 +24372,22 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -24454,12 +24454,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -24536,17 +24536,17 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24556,37 +24556,37 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -24618,57 +24618,57 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -24700,12 +24700,12 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -24735,7 +24735,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -24782,12 +24782,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -24817,7 +24817,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -24864,17 +24864,17 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -24884,12 +24884,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -24946,17 +24946,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24966,12 +24966,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -25028,12 +25028,12 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -25110,17 +25110,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25130,12 +25130,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25170,7 +25170,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -25192,12 +25192,12 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -25274,37 +25274,42 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25319,7 +25324,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25334,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -25351,42 +25356,42 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25401,7 +25406,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25416,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -25433,17 +25438,17 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -25453,12 +25458,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25535,12 +25535,12 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,12 +25617,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,12 +25699,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -25761,12 +25761,12 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -25843,32 +25843,32 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -25925,17 +25925,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -25945,12 +25945,12 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -26007,17 +26007,17 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -26027,37 +26027,37 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -26089,17 +26089,17 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -26109,37 +26109,37 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -26253,39 +26253,39 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26293,17 +26293,17 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -26335,39 +26335,39 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26375,17 +26375,17 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -26417,32 +26417,32 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26457,17 +26457,17 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,12 +26519,12 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26539,17 +26539,17 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26601,12 +26601,12 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -26745,57 +26745,57 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26847,37 +26847,37 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -26909,12 +26909,12 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26991,12 +26991,12 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -27073,32 +27073,32 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -27155,17 +27155,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27175,12 +27175,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -27237,32 +27237,32 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -27319,17 +27319,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27339,12 +27339,12 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -27401,32 +27401,32 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27436,7 +27436,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -27483,17 +27483,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27503,22 +27503,22 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -27565,17 +27565,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27585,22 +27585,22 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -27647,17 +27647,17 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -27729,17 +27729,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -27811,17 +27811,17 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -27893,22 +27893,22 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27953,7 +27953,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -27975,32 +27975,32 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28010,7 +28010,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -28057,12 +28057,12 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -28077,12 +28077,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -28139,42 +28139,42 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -28221,17 +28221,17 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -28241,22 +28241,22 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -28266,22 +28266,12 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28291,7 +28281,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -28313,37 +28303,37 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -28358,22 +28348,12 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28383,7 +28363,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -28405,17 +28385,17 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28425,12 +28405,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28455,7 +28435,17 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28465,7 +28455,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -28487,12 +28477,12 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -28537,7 +28527,17 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -28569,32 +28569,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28614,12 +28614,12 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -28651,32 +28651,32 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -28696,12 +28696,12 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28711,7 +28711,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -28733,12 +28733,12 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -28793,7 +28793,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -28815,27 +28815,32 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -28855,7 +28860,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -28870,7 +28875,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -28892,32 +28897,32 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28937,7 +28942,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -28952,7 +28957,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -28974,42 +28979,37 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -29019,12 +29019,12 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -29056,42 +29056,42 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -29101,12 +29101,12 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -29220,12 +29220,12 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -29240,12 +29240,12 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -29302,17 +29302,17 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -29384,32 +29384,32 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -29429,12 +29429,12 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -29466,12 +29466,12 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -29486,12 +29486,12 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -29548,32 +29548,32 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
@@ -29583,7 +29583,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -29593,12 +29593,12 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -29630,17 +29630,17 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -29680,7 +29680,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -29712,57 +29712,57 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -29794,57 +29794,57 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -29876,7 +29876,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -29896,12 +29896,12 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -29958,7 +29958,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -30018,7 +30018,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -30040,7 +30040,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -30100,7 +30100,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -30122,7 +30122,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -30204,39 +30204,39 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30244,17 +30244,17 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -30286,32 +30286,32 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
@@ -30326,17 +30326,17 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -30368,228 +30368,268 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
+      <c r="E370" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
+      <c r="F370" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
+      <c r="G370" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
+      <c r="H370" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr">
+      <c r="I370" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr">
+      <c r="K370" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L368" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M368" t="inlineStr">
+      <c r="L370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr">
+      <c r="N370" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O368" t="inlineStr">
+      <c r="O370" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R368" t="inlineStr">
+      <c r="R370" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S368" t="inlineStr">
+      <c r="S370" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="E369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="E370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p21</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -30614,14 +30654,14 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -30651,7 +30691,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -30666,7 +30706,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
@@ -30676,19 +30716,19 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -30713,7 +30753,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -30738,19 +30778,19 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -30770,12 +30810,12 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -30790,7 +30830,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
@@ -30800,19 +30840,19 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -30832,12 +30872,12 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -30862,14 +30902,14 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -30899,7 +30939,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -30914,7 +30954,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
@@ -30924,14 +30964,14 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -30961,7 +31001,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -30986,19 +31026,19 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -31008,22 +31048,22 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -31033,7 +31073,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -31048,29 +31088,39 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -31100,19 +31150,24 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="E380" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -31125,6 +31180,11 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31137,7 +31197,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -31152,14 +31212,14 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -31179,7 +31239,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -31204,7 +31264,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -31256,14 +31316,14 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -31308,14 +31368,14 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="E384" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -31325,12 +31385,12 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -31360,14 +31420,14 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="E385" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -31377,12 +31437,12 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -31412,7 +31472,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -31464,62 +31524,166 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="E387" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmmypa-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="E388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="E389" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr">
+      <c r="G389" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
+      <c r="H389" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr">
+      <c r="I389" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr">
+      <c r="K389" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M387" t="inlineStr">
+      <c r="L389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N387" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O387" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R387" t="inlineStr">
+      <c r="N389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S387" t="inlineStr">
+      <c r="S389" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -33371,22 +33535,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gP3</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="E61">
@@ -33402,22 +33551,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="E62">
@@ -33433,12 +33582,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -33448,7 +33597,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E63">
@@ -33464,7 +33613,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -33474,7 +33623,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33495,7 +33644,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -33505,7 +33654,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -33526,7 +33675,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -33536,7 +33685,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -33551,13 +33700,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -33582,13 +33731,13 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -33613,13 +33762,13 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -33644,23 +33793,23 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -33669,7 +33818,7 @@
         </is>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -33681,7 +33830,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -33691,7 +33840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -33712,7 +33861,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -33722,12 +33871,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E72">
@@ -33743,22 +33892,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E73">
@@ -33774,7 +33923,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -33784,12 +33933,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E74">
@@ -33805,7 +33954,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -33815,12 +33964,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E75">
@@ -33836,7 +33985,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33846,12 +33995,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E76">
@@ -33867,7 +34016,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33889,7 +34038,7 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -33898,7 +34047,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -33920,7 +34069,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -33929,7 +34078,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -33939,7 +34088,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -33960,7 +34109,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -33991,7 +34140,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -34013,7 +34162,7 @@
         <v>1</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -34022,7 +34171,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -34044,7 +34193,7 @@
         <v>1</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -34053,7 +34202,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -34084,7 +34233,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -34115,7 +34264,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -34125,7 +34274,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -34146,7 +34295,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -34177,7 +34326,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -34208,7 +34357,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -34218,12 +34367,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E88">
@@ -34239,7 +34388,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -34249,12 +34398,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E89">
@@ -34270,7 +34419,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -34280,12 +34429,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E90">
@@ -34301,7 +34450,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -34311,12 +34460,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E91">
@@ -34332,7 +34481,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -34347,7 +34496,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E92">
@@ -34363,7 +34512,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -34373,7 +34522,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -34394,7 +34543,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -34404,12 +34553,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E94">
@@ -34425,7 +34574,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -34440,7 +34589,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E95">
@@ -34456,7 +34605,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -34487,7 +34636,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -34502,7 +34651,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E97">
@@ -34518,7 +34667,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -34533,7 +34682,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E98">
@@ -34549,7 +34698,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -34564,7 +34713,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E99">
@@ -34580,7 +34729,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -34595,7 +34744,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E100">
@@ -34611,7 +34760,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -34626,7 +34775,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E101">
@@ -34642,7 +34791,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -34657,7 +34806,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E102">
@@ -34673,7 +34822,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -34704,7 +34853,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -34719,7 +34868,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E104">
@@ -34735,7 +34884,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -34745,12 +34894,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E105">
@@ -34766,7 +34915,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -34776,12 +34925,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E106">
@@ -34797,7 +34946,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -34807,12 +34956,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E107">
@@ -34828,17 +34977,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -34859,7 +35008,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -34881,7 +35030,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -34890,7 +35039,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -34912,7 +35061,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -34921,7 +35070,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -34931,7 +35080,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -34952,7 +35101,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -34974,7 +35123,7 @@
         <v>1</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -34983,7 +35132,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -35005,7 +35154,7 @@
         <v>1</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -35014,7 +35163,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -35024,7 +35173,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -35045,7 +35194,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -35076,7 +35225,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -35086,12 +35235,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E116">
@@ -35107,7 +35256,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -35117,12 +35266,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E117">
@@ -35138,7 +35287,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -35153,7 +35302,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E118">
@@ -35169,7 +35318,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -35179,12 +35328,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E119">
@@ -35200,7 +35349,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -35215,7 +35364,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E120">
@@ -35231,7 +35380,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -35246,7 +35395,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E121">
@@ -35262,7 +35411,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -35272,12 +35421,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E122">
@@ -35293,7 +35442,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -35324,7 +35473,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -35339,7 +35488,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E124">
@@ -35355,7 +35504,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -35365,12 +35514,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E125">
@@ -35386,7 +35535,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -35401,7 +35550,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E126">
@@ -35417,7 +35566,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -35448,17 +35597,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C*</t>
+          <t xml:space="preserve">Huh7 lef1 OX</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -35479,7 +35628,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E</t>
+          <t xml:space="preserve">LCC-C*</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -35510,7 +35659,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H</t>
+          <t xml:space="preserve">LCC-E</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -35541,7 +35690,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LCC-H</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -35572,7 +35721,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -35603,7 +35752,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -35634,7 +35783,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -35665,7 +35814,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LNCAP BMK</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -35696,7 +35845,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -35727,7 +35876,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -35758,7 +35907,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -35789,7 +35938,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -35820,7 +35969,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -35851,7 +36000,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -35882,7 +36031,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -35892,7 +36041,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -35913,7 +36062,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -35944,17 +36093,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -35975,7 +36124,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -35985,7 +36139,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E145">
@@ -36001,7 +36155,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -36011,7 +36165,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E146">
@@ -36027,23 +36181,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E147">
+        <v>1</v>
+      </c>
+      <c r="F147">
         <v>0</v>
       </c>
-      <c r="F147">
+      <c r="G147">
         <v>1</v>
-      </c>
-      <c r="G147">
-        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="E148">
@@ -36059,14 +36223,14 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -36075,14 +36239,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -36091,24 +36255,14 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -36117,16 +36271,42 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
+        <v>3</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">klm ox</t>
+        </is>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153">
         <v>1</v>
       </c>
-      <c r="G152">
+      <c r="G153">
         <v>0</v>
       </c>
     </row>
@@ -38213,10 +38393,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20528,17 +20528,17 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p26</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20548,12 +20548,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-mu579vy6-0</t>
         </is>
       </c>
     </row>
@@ -20610,17 +20610,17 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -20630,17 +20630,17 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -20958,12 +20958,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -21020,32 +21020,32 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -21060,17 +21060,17 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21102,39 +21102,39 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21142,17 +21142,17 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21266,17 +21266,17 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -21286,12 +21286,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21306,17 +21306,17 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21348,17 +21348,17 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -21368,17 +21368,17 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -21388,17 +21388,17 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -21450,12 +21450,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21512,17 +21512,17 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -21532,12 +21532,12 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21594,17 +21594,17 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -21629,7 +21629,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -21676,57 +21676,57 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -21758,32 +21758,32 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21840,12 +21840,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -21922,32 +21922,32 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -22024,12 +22024,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22168,32 +22168,37 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -22203,12 +22208,12 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -22223,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22245,12 +22250,12 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -22290,7 +22295,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22300,7 +22305,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22322,17 +22327,17 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -22342,17 +22347,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -22367,12 +22367,12 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22404,7 +22404,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -22414,22 +22414,22 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+24</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fwwc6-0</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22486,7 +22486,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fwwc6-1</t>
+          <t xml:space="preserve">v-mu2fwwc6-0</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fwwc6-2</t>
+          <t xml:space="preserve">v-mu2fwwc6-1</t>
         </is>
       </c>
     </row>
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -22670,12 +22670,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu473zot-0</t>
+          <t xml:space="preserve">v-mu2fwwc6-2</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu473zot-1</t>
+          <t xml:space="preserve">v-mu473zot-0</t>
         </is>
       </c>
     </row>
@@ -22814,12 +22814,12 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu4747r6-0</t>
+          <t xml:space="preserve">v-mu473zot-1</t>
         </is>
       </c>
     </row>
@@ -22896,7 +22896,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu4747r6-1</t>
+          <t xml:space="preserve">v-mu4747r6-0</t>
         </is>
       </c>
     </row>
@@ -22978,12 +22978,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP3</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu474j9w-0</t>
+          <t xml:space="preserve">v-mu4747r6-1</t>
         </is>
       </c>
     </row>
@@ -23060,37 +23060,37 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-0</t>
+          <t xml:space="preserve">v-mu474j9w-0</t>
         </is>
       </c>
     </row>
@@ -23142,7 +23142,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-1</t>
+          <t xml:space="preserve">v-mu2fxi62-0</t>
         </is>
       </c>
     </row>
@@ -23224,7 +23224,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fxi62-2</t>
+          <t xml:space="preserve">v-mu2fxi62-1</t>
         </is>
       </c>
     </row>
@@ -23306,37 +23306,37 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP3</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+24</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu474lbd-0</t>
+          <t xml:space="preserve">v-mu2fxi62-2</t>
         </is>
       </c>
     </row>
@@ -23388,12 +23388,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC1</t>
+          <t xml:space="preserve">LNCX gP3</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">gC1</t>
+          <t xml:space="preserve">gP3</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu474xr1-0</t>
+          <t xml:space="preserve">v-mu474lbd-0</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu474y7n-0</t>
+          <t xml:space="preserve">v-mu474xr1-0</t>
         </is>
       </c>
     </row>
@@ -23552,12 +23552,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC2</t>
+          <t xml:space="preserve">LNCX gC1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">gC2</t>
+          <t xml:space="preserve">gC1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu475zr8-0</t>
+          <t xml:space="preserve">v-mu474y7n-0</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu475zr8-1</t>
+          <t xml:space="preserve">v-mu475zr8-0</t>
         </is>
       </c>
     </row>
@@ -23716,12 +23716,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC3</t>
+          <t xml:space="preserve">LNCX gC2</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">gC3</t>
+          <t xml:space="preserve">gC2</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu4763vn-0</t>
+          <t xml:space="preserve">v-mu475zr8-1</t>
         </is>
       </c>
     </row>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu4763vn-1</t>
+          <t xml:space="preserve">v-mu4763vn-0</t>
         </is>
       </c>
     </row>
@@ -23880,12 +23880,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gC4</t>
+          <t xml:space="preserve">LNCX gC3</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">gC4</t>
+          <t xml:space="preserve">gC3</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu47689b-0</t>
+          <t xml:space="preserve">v-mu4763vn-1</t>
         </is>
       </c>
     </row>
@@ -23962,7 +23962,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">I9</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu47689b-1</t>
+          <t xml:space="preserve">v-mu47689b-0</t>
         </is>
       </c>
     </row>
@@ -24039,42 +24039,42 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX gC4</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">2026-09-16</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -24084,7 +24084,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gC4</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-mu47689b-1</t>
         </is>
       </c>
     </row>
@@ -24126,7 +24126,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -24208,32 +24208,32 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -24290,22 +24290,22 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -24372,7 +24372,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -24454,17 +24454,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -24536,17 +24536,17 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -24618,22 +24618,22 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -24700,32 +24700,32 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -24782,57 +24782,57 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -24864,7 +24864,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -24946,12 +24946,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -25028,7 +25028,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -25110,17 +25110,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25130,12 +25130,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25170,7 +25170,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -25192,17 +25192,17 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25212,12 +25212,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25242,7 +25242,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -25274,17 +25274,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25294,12 +25294,12 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25324,7 +25324,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -25356,12 +25356,12 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -25438,12 +25438,12 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -25520,37 +25520,42 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -25565,7 +25570,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25580,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -25597,7 +25602,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -25607,7 +25612,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,12 +25622,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -25679,12 +25679,12 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -25761,17 +25761,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25781,12 +25781,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25863,12 +25863,12 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -25925,12 +25925,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -26007,12 +26007,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -26171,22 +26171,22 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -26253,57 +26253,57 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -26335,22 +26335,22 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -26417,22 +26417,22 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -26499,39 +26499,39 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26539,17 +26539,17 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -26663,32 +26663,32 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -26703,17 +26703,17 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -26745,22 +26745,22 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -26827,32 +26827,32 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -26909,32 +26909,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27011,37 +27011,37 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -27073,12 +27073,12 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -27155,12 +27155,12 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -27237,12 +27237,12 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -27319,32 +27319,32 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -27401,22 +27401,22 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -27436,7 +27436,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -27483,32 +27483,32 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27518,7 +27518,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -27565,32 +27565,32 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -27647,17 +27647,17 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -27667,12 +27667,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -27729,17 +27729,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -27749,22 +27749,22 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -27893,17 +27893,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27953,7 +27953,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -27975,7 +27975,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -28057,17 +28057,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -28139,22 +28139,22 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -28221,17 +28221,17 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -28313,7 +28313,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28323,12 +28323,12 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -28385,42 +28385,42 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+7</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/5/2025</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -28467,37 +28467,37 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -28512,22 +28512,12 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28537,7 +28527,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -28559,7 +28549,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -28629,7 +28619,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -28651,17 +28641,17 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -28671,12 +28661,12 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -28701,7 +28691,17 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28711,7 +28711,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -28733,7 +28733,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -28743,7 +28743,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28753,12 +28753,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28793,7 +28793,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -28815,32 +28815,32 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -28860,12 +28860,12 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28875,7 +28875,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -28897,12 +28897,12 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -28979,12 +28979,12 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -29039,7 +29039,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -29061,27 +29061,32 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29101,7 +29106,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -29116,7 +29121,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -29138,12 +29143,12 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -29158,12 +29163,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -29220,42 +29220,42 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -29265,12 +29265,12 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -29302,17 +29302,17 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -29322,12 +29322,12 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -29384,17 +29384,17 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -29404,12 +29404,12 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -29466,17 +29466,17 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -29630,32 +29630,32 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -29675,12 +29675,12 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -29712,32 +29712,32 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -29747,7 +29747,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -29757,12 +29757,12 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -29794,17 +29794,17 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -29814,12 +29814,12 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -29844,7 +29844,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -29876,17 +29876,17 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -29896,12 +29896,12 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -29958,57 +29958,57 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -30018,7 +30018,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -30040,7 +30040,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -30050,7 +30050,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -30060,12 +30060,12 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -30100,7 +30100,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -30122,7 +30122,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -30286,7 +30286,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -30450,39 +30450,39 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30490,17 +30490,17 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -30532,22 +30532,22 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -30572,7 +30572,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -30592,7 +30592,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -30614,161 +30614,181 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
+      <c r="E372" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr">
+      <c r="F372" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
+      <c r="G372" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
+      <c r="H372" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr">
+      <c r="I372" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr">
+      <c r="K372" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M371" t="inlineStr">
+      <c r="L372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr">
+      <c r="N372" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O371" t="inlineStr">
+      <c r="O372" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R371" t="inlineStr">
+      <c r="R372" t="inlineStr">
         <is>
           <t xml:space="preserve">stored</t>
         </is>
       </c>
-      <c r="S371" t="inlineStr">
+      <c r="S372" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="E372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-30</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30-06-25</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="L372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-06-30</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">30-06-25</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -30788,7 +30808,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
@@ -30798,14 +30818,14 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-295</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -30835,7 +30855,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -30850,7 +30870,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
@@ -30860,14 +30880,14 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -30897,7 +30917,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -30922,19 +30942,19 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -30959,7 +30979,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -30984,19 +31004,19 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -31016,12 +31036,12 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -31036,7 +31056,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
@@ -31046,19 +31066,19 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdzpx7-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -31083,7 +31103,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -31098,7 +31118,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
@@ -31108,19 +31128,19 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0daw-0</t>
+          <t xml:space="preserve">v-mtrdzpx7-0</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -31145,7 +31165,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -31170,19 +31190,19 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre0daw-0</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="E380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -31207,7 +31227,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -31232,19 +31252,19 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -31254,22 +31274,22 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -31279,7 +31299,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -31294,19 +31314,24 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtski3re-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="E382" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Hek caspex</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -31319,9 +31344,14 @@
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -31331,7 +31361,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -31346,14 +31376,14 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt0h140-0</t>
+          <t xml:space="preserve">v-mtski3re-0</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -31373,7 +31403,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -31398,7 +31428,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-0</t>
+          <t xml:space="preserve">v-mtt0h140-0</t>
         </is>
       </c>
     </row>
@@ -31450,7 +31480,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-1</t>
+          <t xml:space="preserve">v-mtt3mo6u-0</t>
         </is>
       </c>
     </row>
@@ -31502,14 +31532,14 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt3mo6u-2</t>
+          <t xml:space="preserve">v-mtt3mo6u-1</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="E386" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -31554,14 +31584,14 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtt5ckqo-0</t>
+          <t xml:space="preserve">v-mtt3mo6u-2</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="E387" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -31571,12 +31601,12 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -31606,7 +31636,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmw7m-0</t>
+          <t xml:space="preserve">v-mtt5ckqo-0</t>
         </is>
       </c>
     </row>
@@ -31658,7 +31688,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmmypa-0</t>
+          <t xml:space="preserve">v-mttmmw7m-0</t>
         </is>
       </c>
     </row>
@@ -31710,62 +31740,114 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mttmn045-0</t>
+          <t xml:space="preserve">v-mttmmypa-0</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="E390" t="inlineStr">
         <is>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-09</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mttmn045-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="E391" t="inlineStr">
+        <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr">
+      <c r="G391" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
+      <c r="H391" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr">
+      <c r="I391" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr">
+      <c r="K391" t="inlineStr">
         <is>
           <t xml:space="preserve">deneme</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="M390" t="inlineStr">
+      <c r="L391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
         <is>
           <t xml:space="preserve">Par</t>
         </is>
       </c>
-      <c r="N390" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O390" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R390" t="inlineStr">
+      <c r="N391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S390" t="inlineStr">
+      <c r="S391" t="inlineStr">
         <is>
           <t xml:space="preserve">v-mtu5lgdc-0</t>
         </is>
@@ -34098,22 +34180,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">HEK ATF3 KO</t>
         </is>
       </c>
       <c r="E77">
@@ -34129,7 +34196,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34151,7 +34218,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -34160,7 +34227,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34182,7 +34249,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -34191,7 +34258,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -34201,7 +34268,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -34222,7 +34289,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -34253,7 +34320,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -34275,7 +34342,7 @@
         <v>1</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -34284,7 +34351,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -34306,7 +34373,7 @@
         <v>1</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -34315,7 +34382,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -34346,7 +34413,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -34377,7 +34444,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -34387,7 +34454,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -34408,7 +34475,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -34439,7 +34506,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -34470,7 +34537,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -34480,12 +34547,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E89">
@@ -34501,7 +34568,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -34511,12 +34578,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E90">
@@ -34532,7 +34599,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -34542,12 +34609,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E91">
@@ -34563,7 +34630,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -34573,12 +34640,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E92">
@@ -34594,7 +34661,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -34609,7 +34676,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E93">
@@ -34625,7 +34692,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -34635,7 +34702,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -34656,7 +34723,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -34666,12 +34733,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E95">
@@ -34687,7 +34754,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -34702,7 +34769,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E96">
@@ -34718,7 +34785,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -34749,7 +34816,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -34764,7 +34831,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E98">
@@ -34780,7 +34847,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -34795,7 +34862,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E99">
@@ -34811,7 +34878,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -34826,7 +34893,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E100">
@@ -34842,7 +34909,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -34857,7 +34924,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E101">
@@ -34873,7 +34940,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -34888,7 +34955,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E102">
@@ -34904,7 +34971,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -34919,7 +34986,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E103">
@@ -34935,7 +35002,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -34966,7 +35033,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -34981,7 +35048,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E105">
@@ -34997,7 +35064,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -35007,12 +35074,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E106">
@@ -35028,7 +35095,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -35038,12 +35105,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E107">
@@ -35059,7 +35126,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -35069,12 +35136,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E108">
@@ -35090,17 +35157,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -35121,7 +35188,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -35143,7 +35210,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -35152,7 +35219,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -35174,7 +35241,7 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -35183,7 +35250,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -35193,7 +35260,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -35214,7 +35281,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -35236,7 +35303,7 @@
         <v>1</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -35245,7 +35312,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -35267,7 +35334,7 @@
         <v>1</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -35276,7 +35343,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -35286,7 +35353,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -35307,7 +35374,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATF3KO10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -35338,7 +35405,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -35348,12 +35415,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E117">
@@ -35369,7 +35436,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -35379,12 +35446,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E118">
@@ -35400,7 +35467,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -35415,7 +35482,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E119">
@@ -35431,7 +35498,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 CBX3 KO g2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -35441,12 +35508,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E120">
@@ -35462,7 +35529,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -35477,7 +35544,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E121">
@@ -35493,7 +35560,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -35508,7 +35575,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E122">
@@ -35524,7 +35591,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -35534,12 +35601,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E123">
@@ -35555,7 +35622,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -35586,7 +35653,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -35601,7 +35668,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E125">
@@ -35617,7 +35684,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -35627,12 +35694,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E126">
@@ -35648,7 +35715,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -35663,7 +35730,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E127">
@@ -35679,7 +35746,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 OX</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -35710,17 +35777,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C*</t>
+          <t xml:space="preserve">Huh7 lef1 OX</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -35741,7 +35808,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E</t>
+          <t xml:space="preserve">LCC-C*</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -35772,7 +35839,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H</t>
+          <t xml:space="preserve">LCC-E</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -35803,7 +35870,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LCC-H</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -35834,7 +35901,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -35865,7 +35932,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -35896,7 +35963,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -35927,7 +35994,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LNCAP BMK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -35958,7 +36025,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -35989,7 +36056,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -36020,7 +36087,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -36051,7 +36118,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -36082,7 +36149,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -36113,7 +36180,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -36144,7 +36211,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -36154,7 +36221,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -36175,7 +36242,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -36206,17 +36273,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -36237,7 +36304,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -36247,7 +36319,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E146">
@@ -36263,7 +36335,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -36273,7 +36345,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E147">
@@ -36289,23 +36361,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="F148">
         <v>0</v>
       </c>
-      <c r="F148">
+      <c r="G148">
         <v>1</v>
-      </c>
-      <c r="G148">
-        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="E149">
@@ -36321,14 +36403,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -36337,14 +36419,14 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -36353,24 +36435,14 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -36379,16 +36451,42 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E153">
         <v>0</v>
       </c>
       <c r="F153">
+        <v>3</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">klm ox</t>
+        </is>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154">
         <v>1</v>
       </c>
-      <c r="G153">
+      <c r="G154">
         <v>0</v>
       </c>
     </row>
@@ -38475,10 +38573,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J6">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19723,17 +19723,17 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -19743,12 +19743,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -19758,7 +19758,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-1</t>
+          <t xml:space="preserve">v-mu57ag51-0</t>
         </is>
       </c>
     </row>
@@ -19805,12 +19805,12 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -19840,7 +19840,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-1</t>
+          <t xml:space="preserve">v-mtrdxsum-1</t>
         </is>
       </c>
     </row>
@@ -19887,17 +19887,17 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-1</t>
+          <t xml:space="preserve">v-mtrdyhss-1</t>
         </is>
       </c>
     </row>
@@ -19969,37 +19969,42 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p28</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -20024,7 +20029,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-mtrdz1vx-1</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20051,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -20101,7 +20106,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -20123,7 +20128,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -20133,7 +20138,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20143,12 +20148,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -20225,12 +20225,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-11-27</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -20265,7 +20265,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -20307,12 +20307,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -20389,12 +20389,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20471,7 +20471,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-11-06</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20506,7 +20511,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20528,17 +20533,17 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p26</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20548,12 +20553,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-17</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-17</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu579vy6-0</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20610,17 +20610,17 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p26</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -20630,12 +20630,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-mu579vy6-0</t>
         </is>
       </c>
     </row>
@@ -20692,17 +20692,17 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -20712,17 +20712,17 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -21040,12 +21040,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -21102,32 +21102,32 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21142,17 +21142,17 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21184,39 +21184,39 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21224,17 +21224,17 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21348,17 +21348,17 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -21368,12 +21368,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21388,17 +21388,17 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21430,17 +21430,17 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -21450,17 +21450,17 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -21470,17 +21470,17 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -21532,12 +21532,12 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21594,17 +21594,17 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -21614,12 +21614,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -21629,7 +21629,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21676,17 +21676,17 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -21758,57 +21758,57 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -21840,32 +21840,32 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21922,12 +21922,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -22004,32 +22004,32 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -22106,12 +22106,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22250,32 +22250,37 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -22285,12 +22290,12 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -22305,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22327,12 +22332,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -22372,7 +22377,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22382,7 +22387,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22404,17 +22409,17 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -22424,17 +22429,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -22449,12 +22449,12 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22486,7 +22486,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -22496,22 +22496,22 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+24</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-15</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fwwc6-0</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fwwc6-1</t>
+          <t xml:space="preserve">v-mu2fwwc6-0</t>
         </is>
       </c>
     </row>
@@ -22650,7 +22650,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu2fwwc6-2</t>
+          <t xml:space="preserve">v-mu2fwwc6-1</t>
         </is>
       </c>
     </row>
@@ -22732,12 +22732,12 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mu473zot-0</t>
+          <t xml:space="preserve">v-mu2fwwc6-2</t>
         </is